--- a/CEF and SCF formats/CEF_v17.xlsx
+++ b/CEF and SCF formats/CEF_v17.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icesit-my.sharepoint.com/personal/henrikkn_ices_dk/Documents/RDBES/Development/CEF SCF format/2026 02 27 CEF SCF Final uploaded to GitHub public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/kibi_dtu_dk/Documents/RDBES_gits/RDBES/CEF and SCF formats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="357" documentId="13_ncr:1_{76030238-7CD0-4D36-A740-CDFD02C3FDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FC65FFD-BCDA-40F8-8E6F-87E06776423F}"/>
+  <xr:revisionPtr revIDLastSave="367" documentId="13_ncr:1_{76030238-7CD0-4D36-A740-CDFD02C3FDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D97287E9-9EB9-4227-B672-5CFB57E3987B}"/>
   <bookViews>
-    <workbookView xWindow="36" yWindow="528" windowWidth="22812" windowHeight="11436" firstSheet="2" activeTab="6" xr2:uid="{C3BA46FC-17EC-4006-828F-4F15940585FB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3BA46FC-17EC-4006-828F-4F15940585FB}"/>
   </bookViews>
   <sheets>
     <sheet name="CEF" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="307">
   <si>
     <t>Version</t>
   </si>
@@ -647,9 +647,6 @@
     <t>Accepted codes in this field: WeightLive, Number</t>
   </si>
   <si>
-    <t>Accepted codes in this field: das, fd, fe, hf, kWd, NoV, kg/vessel/h</t>
-  </si>
-  <si>
     <t>The calendar year for which fisheries catch data are requested through the data call.</t>
   </si>
   <si>
@@ -1030,111 +1027,117 @@
     <t>The total value of the specified originType and variableType</t>
   </si>
   <si>
-    <t xml:space="preserve">das, fd, fe, hd, hf, kWd, NoV, kg/vessel/h
+    <t>National Information (NI)  for CN and DN</t>
+  </si>
+  <si>
+    <t>Disregard this line only that the below as an example of a National Information file, which have 2 record types the Catch National (CN) and the Distribution National (DN), the order of the CN and DN records does not matter.</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>WGNSSK</t>
+  </si>
+  <si>
+    <t>bll.27.3a47de</t>
+  </si>
+  <si>
+    <t>Quarter</t>
+  </si>
+  <si>
+    <t>27.4.a</t>
+  </si>
+  <si>
+    <t>OTB_DEF_90-119_0_0</t>
+  </si>
+  <si>
+    <t>Fleet</t>
+  </si>
+  <si>
+    <t>OTB_DEF_90-119_0_0_all</t>
+  </si>
+  <si>
+    <t>WGEstimate</t>
+  </si>
+  <si>
+    <t>WeightLive</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>Dis</t>
+  </si>
+  <si>
+    <t>27.7.d</t>
+  </si>
+  <si>
+    <t>TBB_DEF_70-99_0_0</t>
+  </si>
+  <si>
+    <t>TBB_DEF_70-99_0_0_all</t>
+  </si>
+  <si>
+    <t>Official</t>
+  </si>
+  <si>
+    <t>27.3.a; 27.4.a; 27.4.b; 27.4.c; 27.7.e; 27.7.d</t>
+  </si>
+  <si>
+    <t>2023_All_TBB_DEF_70-99_0_0_all</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FishingTrip</t>
+  </si>
+  <si>
+    <t>27.7.e</t>
+  </si>
+  <si>
+    <t>27.4.b</t>
+  </si>
+  <si>
+    <t>27.4.c</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>NE3</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>fishing trip</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">das, fd, fe, hd, hf, kWd-at-sea, kWd-fishing, NoV, kg/vessel/h
 </t>
   </si>
   <si>
-    <t>National Information (NI)  for CN and DN</t>
-  </si>
-  <si>
-    <t>Disregard this line only that the below as an example of a National Information file, which have 2 record types the Catch National (CN) and the Distribution National (DN), the order of the CN and DN records does not matter.</t>
-  </si>
-  <si>
-    <t>BE</t>
-  </si>
-  <si>
-    <t>WGNSSK</t>
-  </si>
-  <si>
-    <t>bll.27.3a47de</t>
-  </si>
-  <si>
-    <t>Quarter</t>
-  </si>
-  <si>
-    <t>27.4.a</t>
-  </si>
-  <si>
-    <t>OTB_DEF_90-119_0_0</t>
-  </si>
-  <si>
-    <t>Fleet</t>
-  </si>
-  <si>
-    <t>OTB_DEF_90-119_0_0_all</t>
-  </si>
-  <si>
-    <t>WGEstimate</t>
-  </si>
-  <si>
-    <t>WeightLive</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>Dis</t>
-  </si>
-  <si>
-    <t>27.7.d</t>
-  </si>
-  <si>
-    <t>TBB_DEF_70-99_0_0</t>
-  </si>
-  <si>
-    <t>TBB_DEF_70-99_0_0_all</t>
-  </si>
-  <si>
-    <t>Official</t>
-  </si>
-  <si>
-    <t>27.3.a; 27.4.a; 27.4.b; 27.4.c; 27.7.e; 27.7.d</t>
-  </si>
-  <si>
-    <t>2023_All_TBB_DEF_70-99_0_0_all</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FishingTrip</t>
-  </si>
-  <si>
-    <t>27.7.e</t>
-  </si>
-  <si>
-    <t>27.4.b</t>
-  </si>
-  <si>
-    <t>27.4.c</t>
-  </si>
-  <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>NE3</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>fishing trip</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>Mean</t>
+    <t>Accepted codes in this field: das, fd, fe, hf, kWd-at-sea, kWd-fishing, NoV, kg/vessel/h</t>
+  </si>
+  <si>
+    <t>Updated accepted codes for EN.variableType</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1235,12 +1238,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Cascadia Mono"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="14"/>
@@ -1378,7 +1375,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1515,8 +1512,7 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1868,26 +1864,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P84"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.6796875" customWidth="1"/>
-    <col min="2" max="2" width="22.6796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.6796875" customWidth="1"/>
-    <col min="5" max="5" width="40.31640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.6796875" customWidth="1"/>
-    <col min="7" max="9" width="5.08984375" customWidth="1"/>
-    <col min="10" max="10" width="33.31640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.6796875" customWidth="1"/>
-    <col min="13" max="13" width="22.6796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="2.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.6796875" customWidth="1"/>
-    <col min="16" max="16" width="27.31640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" customWidth="1"/>
+    <col min="5" max="5" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" customWidth="1"/>
+    <col min="7" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.6640625" customWidth="1"/>
+    <col min="13" max="13" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.6640625" customWidth="1"/>
+    <col min="16" max="16" width="27.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1897,13 +1893,13 @@
       <c r="D2" s="1"/>
       <c r="I2" s="15"/>
     </row>
-    <row r="3" spans="1:16" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="I3" s="15"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="30"/>
       <c r="B4" s="45" t="s">
         <v>144</v>
@@ -1914,7 +1910,7 @@
       <c r="F4" s="31"/>
       <c r="G4" s="32"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="33"/>
       <c r="B5" s="34"/>
       <c r="C5" s="34"/>
@@ -1923,7 +1919,7 @@
       <c r="F5" s="34"/>
       <c r="G5" s="35"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="33"/>
       <c r="B6" s="36" t="s">
         <v>138</v>
@@ -1933,7 +1929,7 @@
       </c>
       <c r="D6" s="34"/>
       <c r="E6" s="36" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F6" s="36" t="s">
         <v>21</v>
@@ -1953,7 +1949,7 @@
       </c>
       <c r="P6" s="17"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="33"/>
       <c r="B7" s="34" t="s">
         <v>46</v>
@@ -1983,7 +1979,7 @@
       </c>
       <c r="P7" s="17"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="33"/>
       <c r="B8" s="34" t="s">
         <v>1</v>
@@ -2013,7 +2009,7 @@
       </c>
       <c r="P8" s="17"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="33"/>
       <c r="B9" s="34" t="s">
         <v>3</v>
@@ -2043,7 +2039,7 @@
       </c>
       <c r="P9" s="17"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="33"/>
       <c r="B10" s="34" t="s">
         <v>4</v>
@@ -2073,7 +2069,7 @@
       </c>
       <c r="P10" s="17"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="33"/>
       <c r="B11" s="34" t="s">
         <v>5</v>
@@ -2103,7 +2099,7 @@
       </c>
       <c r="P11" s="17"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="33"/>
       <c r="B12" s="34" t="s">
         <v>7</v>
@@ -2133,7 +2129,7 @@
       </c>
       <c r="P12" s="17"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="33"/>
       <c r="B13" s="34" t="s">
         <v>9</v>
@@ -2163,7 +2159,7 @@
       </c>
       <c r="P13" s="17"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="33"/>
       <c r="B14" s="34" t="s">
         <v>6</v>
@@ -2193,7 +2189,7 @@
       </c>
       <c r="P14" s="17"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="33"/>
       <c r="B15" s="34" t="s">
         <v>8</v>
@@ -2223,7 +2219,7 @@
       </c>
       <c r="P15" s="17"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="33"/>
       <c r="B16" s="34" t="s">
         <v>10</v>
@@ -2253,7 +2249,7 @@
       </c>
       <c r="P16" s="17"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="33"/>
       <c r="B17" s="34" t="s">
         <v>12</v>
@@ -2283,7 +2279,7 @@
       </c>
       <c r="P17" s="17"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="33"/>
       <c r="B18" s="34" t="s">
         <v>15</v>
@@ -2312,7 +2308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="33"/>
       <c r="B19" s="34" t="s">
         <v>17</v>
@@ -2335,13 +2331,13 @@
         <v>2</v>
       </c>
       <c r="M19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N19" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="33"/>
       <c r="B20" s="34" t="s">
         <v>18</v>
@@ -2370,7 +2366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="33"/>
       <c r="B21" s="34" t="s">
         <v>20</v>
@@ -2399,7 +2395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="33"/>
       <c r="B22" s="34" t="s">
         <v>28</v>
@@ -2422,7 +2418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="33"/>
       <c r="B23" s="34" t="s">
         <v>30</v>
@@ -2445,7 +2441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="33"/>
       <c r="B24" s="34" t="s">
         <v>11</v>
@@ -2462,16 +2458,16 @@
       </c>
       <c r="G24" s="35"/>
       <c r="J24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K24" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="33"/>
       <c r="B25" s="34" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C25" s="34" t="s">
         <v>2</v>
@@ -2491,7 +2487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="33"/>
       <c r="B26" s="34" t="s">
         <v>26</v>
@@ -2515,7 +2511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="33"/>
       <c r="B27" s="39" t="s">
         <v>29</v>
@@ -2539,7 +2535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="33"/>
       <c r="B28" s="39" t="s">
         <v>27</v>
@@ -2557,7 +2553,7 @@
       <c r="G28" s="38"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="33"/>
       <c r="B29" s="39" t="s">
         <v>33</v>
@@ -2576,7 +2572,7 @@
       <c r="I29" s="1"/>
       <c r="L29" s="12"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="33"/>
       <c r="B30" s="39" t="s">
         <v>34</v>
@@ -2590,7 +2586,7 @@
       <c r="G30" s="35"/>
       <c r="I30" s="17"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="33"/>
       <c r="B31" s="34" t="s">
         <v>35</v>
@@ -2604,7 +2600,7 @@
       <c r="G31" s="35"/>
       <c r="I31" s="17"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="33"/>
       <c r="B32" s="34" t="s">
         <v>36</v>
@@ -2618,7 +2614,7 @@
       <c r="G32" s="35"/>
       <c r="I32" s="17"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="33"/>
       <c r="B33" s="34" t="s">
         <v>38</v>
@@ -2632,7 +2628,7 @@
       <c r="G33" s="35"/>
       <c r="I33" s="17"/>
     </row>
-    <row r="34" spans="1:9" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="34" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="41"/>
       <c r="B34" s="42"/>
       <c r="C34" s="43"/>
@@ -2642,68 +2638,68 @@
       <c r="G34" s="44"/>
       <c r="I34" s="17"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
       <c r="I35" s="17"/>
     </row>
-    <row r="50" spans="10:13" x14ac:dyDescent="0.75">
+    <row r="50" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J50" s="17"/>
     </row>
-    <row r="52" spans="10:13" x14ac:dyDescent="0.75">
+    <row r="52" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J52" s="12"/>
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
       <c r="M52" s="18"/>
     </row>
-    <row r="53" spans="10:13" x14ac:dyDescent="0.75">
+    <row r="53" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J53" s="12"/>
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="10:13" x14ac:dyDescent="0.75">
+    <row r="54" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J54" s="12"/>
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="10:13" x14ac:dyDescent="0.75">
+    <row r="55" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J55" s="12"/>
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="10:13" x14ac:dyDescent="0.75">
+    <row r="56" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J56" s="12"/>
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="10:13" x14ac:dyDescent="0.75">
+    <row r="57" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J57" s="12"/>
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="10:13" x14ac:dyDescent="0.75">
+    <row r="58" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J58" s="12"/>
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="10:13" x14ac:dyDescent="0.75">
+    <row r="59" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J59" s="12"/>
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="80" spans="11:11" x14ac:dyDescent="0.75">
+    <row r="80" spans="11:11" x14ac:dyDescent="0.3">
       <c r="K80" s="12"/>
     </row>
-    <row r="81" spans="11:11" x14ac:dyDescent="0.75">
+    <row r="81" spans="11:11" x14ac:dyDescent="0.3">
       <c r="K81" s="12"/>
     </row>
-    <row r="82" spans="11:11" x14ac:dyDescent="0.75">
+    <row r="82" spans="11:11" x14ac:dyDescent="0.3">
       <c r="K82" s="17"/>
     </row>
-    <row r="83" spans="11:11" x14ac:dyDescent="0.75">
+    <row r="83" spans="11:11" x14ac:dyDescent="0.3">
       <c r="K83" s="17"/>
     </row>
-    <row r="84" spans="11:11" x14ac:dyDescent="0.75">
+    <row r="84" spans="11:11" x14ac:dyDescent="0.3">
       <c r="K84" s="17"/>
     </row>
   </sheetData>
@@ -2715,30 +2711,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.08984375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="15.109375" style="6" customWidth="1"/>
     <col min="2" max="2" width="19" style="6" customWidth="1"/>
     <col min="3" max="3" width="27" style="6" customWidth="1"/>
-    <col min="4" max="4" width="10.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.08984375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="15.31640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.31640625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="29.86328125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="30.08984375" style="7" customWidth="1"/>
-    <col min="10" max="10" width="28.31640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="77.31640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="113.31640625" style="7" customWidth="1"/>
-    <col min="13" max="13" width="113.31640625" style="6" customWidth="1"/>
-    <col min="14" max="16384" width="8.6796875" style="6"/>
+    <col min="4" max="4" width="10.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="29.88671875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="30.109375" style="7" customWidth="1"/>
+    <col min="10" max="10" width="28.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="77.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="113.33203125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="113.33203125" style="6" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>146</v>
       </c>
@@ -2777,7 +2773,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3" s="13"/>
       <c r="C3" s="4" t="s">
         <v>46</v>
@@ -2802,7 +2798,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>50</v>
       </c>
@@ -2835,7 +2831,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>50</v>
       </c>
@@ -2862,13 +2858,13 @@
       </c>
       <c r="I5" s="6"/>
       <c r="K5" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>50</v>
       </c>
@@ -2902,7 +2898,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>50</v>
       </c>
@@ -2930,13 +2926,13 @@
       <c r="I7" s="24"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="59" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>50</v>
       </c>
@@ -2969,7 +2965,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="177" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>50</v>
       </c>
@@ -2999,13 +2995,13 @@
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="59" x14ac:dyDescent="0.75">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>51</v>
       </c>
@@ -3028,17 +3024,17 @@
         <v>110</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="147.5" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="B11" s="6" t="s">
         <v>51</v>
       </c>
@@ -3062,13 +3058,13 @@
       </c>
       <c r="I11" s="20"/>
       <c r="K11" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.75">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>51</v>
       </c>
@@ -3100,7 +3096,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>51</v>
       </c>
@@ -3124,13 +3120,13 @@
       </c>
       <c r="I13" s="6"/>
       <c r="K13" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="L13" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="L13" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="59" x14ac:dyDescent="0.75">
+    </row>
+    <row r="14" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
         <v>51</v>
       </c>
@@ -3160,7 +3156,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>51</v>
       </c>
@@ -3184,13 +3180,13 @@
       </c>
       <c r="I15" s="6"/>
       <c r="K15" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="L15" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="L15" s="7" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="103.25" x14ac:dyDescent="0.75">
+    </row>
+    <row r="16" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
         <v>51</v>
       </c>
@@ -3207,21 +3203,21 @@
         <v>52</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
       <c r="K16" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="147.5" x14ac:dyDescent="0.75">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="144" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>51</v>
       </c>
@@ -3238,19 +3234,19 @@
         <v>52</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="L17" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="L17" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="185.4" customHeight="1" x14ac:dyDescent="0.75">
+    </row>
+    <row r="18" spans="1:12" ht="185.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="4" t="s">
         <v>28</v>
       </c>
@@ -3267,13 +3263,13 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="K18" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="185.4" customHeight="1" x14ac:dyDescent="0.75">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="185.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="4" t="s">
         <v>30</v>
       </c>
@@ -3290,13 +3286,13 @@
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="K19" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="132.75" x14ac:dyDescent="0.75">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>50</v>
       </c>
@@ -3316,18 +3312,18 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="K20" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="132.75" x14ac:dyDescent="0.75">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>47</v>
@@ -3349,13 +3345,13 @@
       </c>
       <c r="J21" s="14"/>
       <c r="K21" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L21" s="29" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="29.5" x14ac:dyDescent="0.45">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="28.8" x14ac:dyDescent="0.2">
       <c r="B22" s="6" t="s">
         <v>51</v>
       </c>
@@ -3385,10 +3381,10 @@
         <v>167</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="59" x14ac:dyDescent="0.75">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C23" s="4" t="s">
         <v>29</v>
       </c>
@@ -3412,13 +3408,13 @@
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="118" x14ac:dyDescent="0.75">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
       <c r="C24" s="4" t="s">
         <v>27</v>
       </c>
@@ -3429,19 +3425,19 @@
         <v>2</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="K24" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.75">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C25" s="4" t="s">
         <v>33</v>
       </c>
@@ -3461,7 +3457,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="88.5" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C26" s="4" t="s">
         <v>34</v>
       </c>
@@ -3481,17 +3477,17 @@
         <v>117</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J26" s="14"/>
       <c r="K26" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="44.25" x14ac:dyDescent="0.75">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C27" s="4" t="s">
         <v>35</v>
       </c>
@@ -3506,13 +3502,13 @@
       </c>
       <c r="G27" s="7"/>
       <c r="K27" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="44.25" x14ac:dyDescent="0.75">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C28" s="4" t="s">
         <v>36</v>
       </c>
@@ -3527,13 +3523,13 @@
       </c>
       <c r="G28" s="7"/>
       <c r="K28" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="29.5" x14ac:dyDescent="0.75">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C29" s="4" t="s">
         <v>38</v>
       </c>
@@ -3560,23 +3556,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:O25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.6796875" style="6"/>
-    <col min="2" max="2" width="20.6796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6796875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="4.6796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="6"/>
+    <col min="2" max="2" width="20.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="4.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26" style="3" customWidth="1"/>
-    <col min="7" max="7" width="38.6796875" style="2" customWidth="1"/>
-    <col min="8" max="9" width="26.453125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="72.86328125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="90.86328125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="71.31640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6796875" style="2"/>
+    <col min="7" max="7" width="38.6640625" style="2" customWidth="1"/>
+    <col min="8" max="9" width="26.44140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="72.88671875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="90.88671875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="71.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>139</v>
       </c>
@@ -3592,7 +3588,7 @@
       <c r="K1" s="7"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>145</v>
       </c>
@@ -3630,7 +3626,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C3" s="4" t="s">
         <v>46</v>
       </c>
@@ -3660,7 +3656,7 @@
       </c>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" spans="1:15" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>50</v>
       </c>
@@ -3694,7 +3690,7 @@
       </c>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>50</v>
       </c>
@@ -3721,14 +3717,14 @@
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>143</v>
       </c>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>50</v>
       </c>
@@ -3762,7 +3758,7 @@
       </c>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>50</v>
       </c>
@@ -3788,14 +3784,14 @@
         <v>109</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>143</v>
       </c>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="1:15" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>50</v>
       </c>
@@ -3829,7 +3825,7 @@
       </c>
       <c r="L8" s="7"/>
     </row>
-    <row r="9" spans="1:15" ht="59" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>50</v>
       </c>
@@ -3858,14 +3854,14 @@
         <v>154</v>
       </c>
       <c r="J9" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>191</v>
-      </c>
       <c r="L9" s="7"/>
     </row>
-    <row r="10" spans="1:15" ht="103.25" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>50</v>
       </c>
@@ -3886,14 +3882,14 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>150</v>
       </c>
       <c r="L10" s="7"/>
     </row>
-    <row r="11" spans="1:15" ht="103.25" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B11" s="6" t="s">
         <v>51</v>
       </c>
@@ -3919,14 +3915,14 @@
         <v>158</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L11" s="7"/>
     </row>
-    <row r="12" spans="1:15" ht="103.25" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B12" s="51"/>
       <c r="C12" s="4" t="s">
         <v>16</v>
@@ -3950,14 +3946,14 @@
         <v>159</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" spans="1:15" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>51</v>
       </c>
@@ -3980,7 +3976,7 @@
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
     </row>
-    <row r="14" spans="1:15" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:15" ht="72" x14ac:dyDescent="0.3">
       <c r="B14" s="51"/>
       <c r="C14" s="4" t="s">
         <v>19</v>
@@ -3996,14 +3992,14 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L14" s="7"/>
     </row>
-    <row r="15" spans="1:15" s="14" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:15" s="14" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6" t="s">
         <v>51</v>
@@ -4030,14 +4026,14 @@
         <v>160</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L15" s="5"/>
     </row>
-    <row r="16" spans="1:15" s="14" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:15" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6" t="s">
         <v>51</v>
@@ -4064,14 +4060,14 @@
         <v>161</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L16" s="5"/>
     </row>
-    <row r="17" spans="2:12" ht="106.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="17" spans="2:12" ht="106.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>51</v>
       </c>
@@ -4094,17 +4090,17 @@
         <v>115</v>
       </c>
       <c r="I17" s="48" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L17" s="7"/>
     </row>
-    <row r="18" spans="2:12" ht="88.5" x14ac:dyDescent="0.75">
+    <row r="18" spans="2:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B18" s="6"/>
       <c r="C18" s="4" t="s">
         <v>29</v>
@@ -4128,14 +4124,14 @@
         <v>162</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L18" s="7"/>
     </row>
-    <row r="19" spans="2:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="19" spans="2:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="51"/>
       <c r="C19" s="4" t="s">
         <v>31</v>
@@ -4159,14 +4155,14 @@
         <v>163</v>
       </c>
       <c r="J19" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K19" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>217</v>
-      </c>
       <c r="L19" s="7"/>
     </row>
-    <row r="20" spans="2:12" ht="88.5" x14ac:dyDescent="0.75">
+    <row r="20" spans="2:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B20" s="6"/>
       <c r="C20" s="4" t="s">
         <v>32</v>
@@ -4181,12 +4177,12 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.75">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="6"/>
       <c r="C21" s="4" t="s">
         <v>33</v>
@@ -4207,7 +4203,7 @@
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
-    <row r="22" spans="2:12" ht="103.25" x14ac:dyDescent="0.75">
+    <row r="22" spans="2:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B22" s="6"/>
       <c r="C22" s="4" t="s">
         <v>34</v>
@@ -4228,17 +4224,17 @@
         <v>117</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J22" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="K22" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="K22" s="7" t="s">
-        <v>241</v>
-      </c>
       <c r="L22" s="7"/>
     </row>
-    <row r="23" spans="2:12" ht="59" x14ac:dyDescent="0.75">
+    <row r="23" spans="2:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B23" s="6"/>
       <c r="C23" s="4" t="s">
         <v>35</v>
@@ -4256,12 +4252,12 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
     </row>
-    <row r="24" spans="2:12" ht="128.25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="24" spans="2:12" ht="128.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="6"/>
       <c r="C24" s="4" t="s">
         <v>36</v>
@@ -4279,14 +4275,14 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L24" s="7"/>
     </row>
-    <row r="25" spans="2:12" ht="88.5" x14ac:dyDescent="0.75">
+    <row r="25" spans="2:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B25" s="6"/>
       <c r="C25" s="4" t="s">
         <v>37</v>
@@ -4304,7 +4300,7 @@
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
       <c r="J25" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -4318,22 +4314,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="34.453125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="13.31640625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="34.44140625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="11" customWidth="1"/>
     <col min="4" max="4" width="11" style="11" customWidth="1"/>
-    <col min="5" max="5" width="17.453125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" style="11" customWidth="1"/>
     <col min="6" max="6" width="35" style="11" customWidth="1"/>
-    <col min="7" max="7" width="40.31640625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="48.54296875" style="11" customWidth="1"/>
-    <col min="9" max="9" width="80.453125" style="11" customWidth="1"/>
-    <col min="10" max="11" width="67.31640625" style="11" customWidth="1"/>
-    <col min="12" max="16384" width="8.6796875" style="11"/>
+    <col min="7" max="7" width="40.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="48.5546875" style="11" customWidth="1"/>
+    <col min="9" max="9" width="80.44140625" style="11" customWidth="1"/>
+    <col min="10" max="11" width="67.33203125" style="11" customWidth="1"/>
+    <col min="12" max="16384" width="8.6640625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="49" t="s">
         <v>75</v>
       </c>
@@ -4349,7 +4345,7 @@
       <c r="K1" s="27"/>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="49" t="s">
         <v>76</v>
       </c>
@@ -4365,7 +4361,7 @@
       <c r="K2" s="27"/>
       <c r="L2" s="27"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="49" t="s">
         <v>77</v>
       </c>
@@ -4381,7 +4377,7 @@
       <c r="K3" s="27"/>
       <c r="L3" s="27"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>137</v>
       </c>
@@ -4397,7 +4393,7 @@
       <c r="K4" s="27"/>
       <c r="L4" s="27"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>60</v>
       </c>
@@ -4433,7 +4429,7 @@
       </c>
       <c r="L5" s="27"/>
     </row>
-    <row r="6" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13"/>
       <c r="B6" s="4" t="s">
         <v>46</v>
@@ -4464,7 +4460,7 @@
       </c>
       <c r="M6" s="16"/>
     </row>
-    <row r="7" spans="1:13" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>51</v>
       </c>
@@ -4496,7 +4492,7 @@
       <c r="K7" s="6"/>
       <c r="L7" s="27"/>
     </row>
-    <row r="8" spans="1:13" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>51</v>
       </c>
@@ -4520,7 +4516,7 @@
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>143</v>
@@ -4528,7 +4524,7 @@
       <c r="K8" s="6"/>
       <c r="L8" s="27"/>
     </row>
-    <row r="9" spans="1:13" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>51</v>
       </c>
@@ -4562,7 +4558,7 @@
       </c>
       <c r="L9" s="27"/>
     </row>
-    <row r="10" spans="1:13" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>51</v>
       </c>
@@ -4586,7 +4582,7 @@
       </c>
       <c r="H10" s="24"/>
       <c r="I10" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>143</v>
@@ -4594,7 +4590,7 @@
       <c r="K10" s="6"/>
       <c r="L10" s="27"/>
     </row>
-    <row r="11" spans="1:13" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>51</v>
       </c>
@@ -4626,7 +4622,7 @@
       <c r="K11" s="6"/>
       <c r="L11" s="27"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>51</v>
       </c>
@@ -4652,7 +4648,7 @@
         <v>169</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>171</v>
@@ -4660,7 +4656,7 @@
       <c r="K12" s="6"/>
       <c r="L12" s="27"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>51</v>
       </c>
@@ -4677,16 +4673,16 @@
         <v>52</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>110</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J13" s="26" t="s">
         <v>172</v>
@@ -4694,7 +4690,7 @@
       <c r="K13" s="6"/>
       <c r="L13" s="27"/>
     </row>
-    <row r="14" spans="1:13" ht="118" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>51</v>
       </c>
@@ -4718,15 +4714,15 @@
       </c>
       <c r="H14" s="20"/>
       <c r="I14" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="27"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="4" t="s">
         <v>10</v>
@@ -4758,7 +4754,7 @@
       <c r="K15" s="6"/>
       <c r="L15" s="27"/>
     </row>
-    <row r="16" spans="1:13" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>51</v>
       </c>
@@ -4782,15 +4778,15 @@
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="54" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="27"/>
     </row>
-    <row r="17" spans="1:12" ht="59" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>51</v>
       </c>
@@ -4822,7 +4818,7 @@
       <c r="K17" s="6"/>
       <c r="L17" s="27"/>
     </row>
-    <row r="18" spans="1:12" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>51</v>
       </c>
@@ -4854,7 +4850,7 @@
       <c r="K18" s="6"/>
       <c r="L18" s="27"/>
     </row>
-    <row r="19" spans="1:12" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>51</v>
       </c>
@@ -4871,24 +4867,24 @@
         <v>52</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>126</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>84</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="27"/>
     </row>
-    <row r="20" spans="1:12" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>51</v>
       </c>
@@ -4920,7 +4916,7 @@
       <c r="K20" s="6"/>
       <c r="L20" s="27"/>
     </row>
-    <row r="21" spans="1:12" ht="59" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>51</v>
       </c>
@@ -4937,20 +4933,20 @@
         <v>52</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
       <c r="L21" s="27"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>51</v>
       </c>
@@ -4972,7 +4968,7 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>128</v>
@@ -4980,12 +4976,12 @@
       <c r="K22" s="6"/>
       <c r="L22" s="27"/>
     </row>
-    <row r="23" spans="1:12" s="6" customFormat="1" ht="59" x14ac:dyDescent="0.7">
+    <row r="23" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="57" t="s">
-        <v>251</v>
+      <c r="B23" s="4" t="s">
+        <v>250</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>47</v>
@@ -5006,14 +5002,14 @@
         <v>157</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>175</v>
       </c>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>51</v>
       </c>
@@ -5047,7 +5043,7 @@
       <c r="K24" s="6"/>
       <c r="L24" s="27"/>
     </row>
-    <row r="25" spans="1:12" ht="59" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="52"/>
       <c r="B25" s="4" t="s">
         <v>29</v>
@@ -5071,15 +5067,15 @@
         <v>156</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K25" s="27"/>
       <c r="L25" s="27"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="27"/>
       <c r="B26" s="4" t="s">
         <v>27</v>
@@ -5091,13 +5087,13 @@
         <v>2</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="27"/>
       <c r="H26" s="27"/>
       <c r="I26" s="27" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J26" s="27"/>
       <c r="K26" s="27"/>
@@ -5111,23 +5107,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.31640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.31640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.6796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6796875" style="11" customWidth="1"/>
-    <col min="6" max="6" width="27.6796875" style="11" customWidth="1"/>
-    <col min="7" max="7" width="26.54296875" style="11" customWidth="1"/>
-    <col min="8" max="8" width="36.31640625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="74.54296875" style="11" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" style="11" customWidth="1"/>
+    <col min="6" max="6" width="27.6640625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="26.5546875" style="11" customWidth="1"/>
+    <col min="8" max="8" width="36.33203125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="74.5546875" style="11" customWidth="1"/>
     <col min="10" max="10" width="69" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="86" style="11" customWidth="1"/>
-    <col min="12" max="16384" width="8.6796875" style="11"/>
+    <col min="12" max="16384" width="8.6640625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>136</v>
       </c>
@@ -5135,7 +5131,7 @@
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
     </row>
-    <row r="2" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>60</v>
       </c>
@@ -5170,7 +5166,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
       <c r="B3" s="4" t="s">
         <v>46</v>
@@ -5201,7 +5197,7 @@
       </c>
       <c r="M3" s="16"/>
     </row>
-    <row r="4" spans="1:13" s="6" customFormat="1" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:13" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>51</v>
       </c>
@@ -5232,7 +5228,7 @@
       </c>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:13" s="6" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:13" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>51</v>
       </c>
@@ -5256,14 +5252,14 @@
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>143</v>
       </c>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:13" s="6" customFormat="1" ht="84.45" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:13" s="6" customFormat="1" ht="84.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>51</v>
       </c>
@@ -5296,7 +5292,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>51</v>
       </c>
@@ -5313,23 +5309,23 @@
         <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>110</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J7" s="26" t="s">
         <v>172</v>
       </c>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:13" s="6" customFormat="1" ht="103.25" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:13" s="6" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>51</v>
       </c>
@@ -5353,14 +5349,14 @@
       </c>
       <c r="H8" s="20"/>
       <c r="I8" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>51</v>
       </c>
@@ -5393,7 +5389,7 @@
       </c>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:13" s="6" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:13" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>51</v>
       </c>
@@ -5416,14 +5412,14 @@
         <v>113</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:13" s="6" customFormat="1" ht="59" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:13" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>51</v>
       </c>
@@ -5454,7 +5450,7 @@
       </c>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:13" s="6" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:13" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>51</v>
       </c>
@@ -5484,7 +5480,7 @@
       </c>
       <c r="K12" s="7"/>
     </row>
-    <row r="13" spans="1:13" s="6" customFormat="1" ht="59" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:13" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>51</v>
       </c>
@@ -5501,19 +5497,19 @@
         <v>52</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J13" s="46"/>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>51</v>
       </c>
@@ -5535,17 +5531,17 @@
       <c r="G14" s="5"/>
       <c r="H14" s="14"/>
       <c r="I14" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J14" s="28"/>
       <c r="K14" s="7"/>
     </row>
-    <row r="15" spans="1:13" s="6" customFormat="1" ht="29.5" x14ac:dyDescent="0.7">
+    <row r="15" spans="1:13" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="57" t="s">
-        <v>251</v>
+      <c r="B15" s="4" t="s">
+        <v>250</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>47</v>
@@ -5566,14 +5562,14 @@
         <v>157</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>175</v>
       </c>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:13" s="6" customFormat="1" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:13" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>51</v>
       </c>
@@ -5596,17 +5592,17 @@
         <v>116</v>
       </c>
       <c r="H16" s="55" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>177</v>
+        <v>305</v>
       </c>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="27"/>
       <c r="B17" s="4" t="s">
         <v>27</v>
@@ -5618,13 +5614,13 @@
         <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F17" s="27"/>
       <c r="G17" s="27"/>
       <c r="H17" s="27"/>
       <c r="I17" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="27"/>
@@ -5638,88 +5634,88 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64892F72-1763-401F-9D26-6A585AD066D9}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.86328125" customWidth="1"/>
+    <col min="1" max="1" width="38.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>4</v>
       </c>
@@ -5732,28 +5728,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26B2173E-E90A-492C-9D22-C3FF9006981E}">
   <dimension ref="A1:AA37"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="19" x14ac:dyDescent="0.95">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C2">
         <v>2023</v>
       </c>
       <c r="D2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F2">
         <v>127150</v>
@@ -5762,7 +5758,7 @@
         <v>169</v>
       </c>
       <c r="H2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -5771,60 +5767,60 @@
         <v>93</v>
       </c>
       <c r="K2" t="s">
+        <v>278</v>
+      </c>
+      <c r="L2" s="57"/>
+      <c r="M2" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="N2" t="s">
         <v>280</v>
       </c>
-      <c r="L2" s="58"/>
-      <c r="M2" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" t="s">
         <v>282</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="T2" s="57" t="s">
         <v>283</v>
       </c>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" t="s">
+      <c r="U2" s="57" t="s">
         <v>284</v>
       </c>
-      <c r="T2" s="58" t="s">
-        <v>285</v>
-      </c>
-      <c r="U2" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="V2" s="59">
+      <c r="V2" s="58">
         <v>377</v>
       </c>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="58"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="58"/>
-    </row>
-    <row r="3" spans="1:27" ht="19" x14ac:dyDescent="0.95">
+      <c r="W2" s="58"/>
+      <c r="X2" s="58"/>
+      <c r="Y2" s="57"/>
+      <c r="Z2" s="58"/>
+      <c r="AA2" s="57"/>
+    </row>
+    <row r="3" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C3">
         <v>2023</v>
       </c>
       <c r="D3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F3">
         <v>127150</v>
       </c>
       <c r="G3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H3" t="s">
         <v>96</v>
@@ -5836,57 +5832,57 @@
         <v>93</v>
       </c>
       <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="M3" t="s">
+        <v>287</v>
+      </c>
+      <c r="N3" t="s">
+        <v>280</v>
+      </c>
+      <c r="O3" t="s">
         <v>288</v>
-      </c>
-      <c r="M3" t="s">
-        <v>289</v>
-      </c>
-      <c r="N3" t="s">
-        <v>282</v>
-      </c>
-      <c r="O3" t="s">
-        <v>290</v>
       </c>
       <c r="P3" s="1"/>
       <c r="S3" t="s">
-        <v>291</v>
-      </c>
-      <c r="T3" s="58" t="s">
-        <v>285</v>
-      </c>
-      <c r="U3" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="V3" s="59">
+        <v>289</v>
+      </c>
+      <c r="T3" s="57" t="s">
+        <v>283</v>
+      </c>
+      <c r="U3" s="57" t="s">
+        <v>284</v>
+      </c>
+      <c r="V3" s="58">
         <v>15</v>
       </c>
-      <c r="W3" s="59"/>
-      <c r="X3" s="59"/>
-      <c r="Y3" s="58"/>
-      <c r="Z3" s="59"/>
-      <c r="AA3" s="58"/>
-    </row>
-    <row r="4" spans="1:27" ht="19" x14ac:dyDescent="0.95">
+      <c r="W3" s="58"/>
+      <c r="X3" s="58"/>
+      <c r="Y3" s="57"/>
+      <c r="Z3" s="58"/>
+      <c r="AA3" s="57"/>
+    </row>
+    <row r="4" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C4">
         <v>2023</v>
       </c>
       <c r="D4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F4">
         <v>127150</v>
       </c>
       <c r="G4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H4" t="s">
         <v>96</v>
@@ -5898,60 +5894,60 @@
         <v>93</v>
       </c>
       <c r="K4" t="s">
+        <v>290</v>
+      </c>
+      <c r="M4" t="s">
+        <v>287</v>
+      </c>
+      <c r="N4" t="s">
+        <v>280</v>
+      </c>
+      <c r="O4" t="s">
+        <v>288</v>
+      </c>
+      <c r="P4" t="s">
+        <v>291</v>
+      </c>
+      <c r="R4" t="s">
+        <v>291</v>
+      </c>
+      <c r="S4" t="s">
+        <v>282</v>
+      </c>
+      <c r="T4" s="57" t="s">
+        <v>283</v>
+      </c>
+      <c r="U4" s="57" t="s">
+        <v>284</v>
+      </c>
+      <c r="V4" s="59">
+        <v>250</v>
+      </c>
+      <c r="X4" s="59" t="s">
         <v>292</v>
       </c>
-      <c r="M4" t="s">
-        <v>289</v>
-      </c>
-      <c r="N4" t="s">
-        <v>282</v>
-      </c>
-      <c r="O4" t="s">
-        <v>290</v>
-      </c>
-      <c r="P4" t="s">
-        <v>293</v>
-      </c>
-      <c r="R4" t="s">
-        <v>293</v>
-      </c>
-      <c r="S4" t="s">
-        <v>284</v>
-      </c>
-      <c r="T4" s="58" t="s">
-        <v>285</v>
-      </c>
-      <c r="U4" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="V4" s="60">
-        <v>250</v>
-      </c>
-      <c r="X4" s="60" t="s">
-        <v>294</v>
-      </c>
-      <c r="Y4" s="60">
+      <c r="Y4" s="59">
         <v>15</v>
       </c>
-      <c r="Z4" s="60">
+      <c r="Z4" s="59">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19" x14ac:dyDescent="0.95">
+    <row r="5" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C5">
         <v>2023</v>
       </c>
       <c r="D5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F5">
         <v>127150</v>
@@ -5969,52 +5965,52 @@
         <v>93</v>
       </c>
       <c r="K5" t="s">
+        <v>286</v>
+      </c>
+      <c r="M5" t="s">
+        <v>287</v>
+      </c>
+      <c r="N5" t="s">
+        <v>280</v>
+      </c>
+      <c r="O5" t="s">
         <v>288</v>
       </c>
-      <c r="M5" t="s">
-        <v>289</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="P5" t="s">
+        <v>291</v>
+      </c>
+      <c r="R5" t="s">
+        <v>291</v>
+      </c>
+      <c r="S5" t="s">
         <v>282</v>
       </c>
-      <c r="O5" t="s">
-        <v>290</v>
-      </c>
-      <c r="P5" t="s">
-        <v>293</v>
-      </c>
-      <c r="R5" t="s">
-        <v>293</v>
-      </c>
-      <c r="S5" t="s">
+      <c r="T5" s="57" t="s">
+        <v>283</v>
+      </c>
+      <c r="U5" s="57" t="s">
         <v>284</v>
       </c>
-      <c r="T5" s="58" t="s">
-        <v>285</v>
-      </c>
-      <c r="U5" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="V5" s="60">
+      <c r="V5" s="59">
         <v>523</v>
       </c>
-      <c r="W5" s="60"/>
-    </row>
-    <row r="6" spans="1:27" ht="19" x14ac:dyDescent="0.95">
+      <c r="W5" s="59"/>
+    </row>
+    <row r="6" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C6">
         <v>2023</v>
       </c>
       <c r="D6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F6">
         <v>127150</v>
@@ -6032,52 +6028,52 @@
         <v>93</v>
       </c>
       <c r="K6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="N6" t="s">
+        <v>280</v>
+      </c>
+      <c r="O6" t="s">
+        <v>288</v>
+      </c>
+      <c r="P6" t="s">
+        <v>291</v>
+      </c>
+      <c r="R6" t="s">
+        <v>291</v>
+      </c>
+      <c r="S6" t="s">
         <v>282</v>
       </c>
-      <c r="O6" t="s">
-        <v>290</v>
-      </c>
-      <c r="P6" t="s">
-        <v>293</v>
-      </c>
-      <c r="R6" t="s">
-        <v>293</v>
-      </c>
-      <c r="S6" t="s">
+      <c r="T6" s="57" t="s">
+        <v>283</v>
+      </c>
+      <c r="U6" s="57" t="s">
         <v>284</v>
       </c>
-      <c r="T6" s="58" t="s">
-        <v>285</v>
-      </c>
-      <c r="U6" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="V6" s="60">
+      <c r="V6" s="59">
         <v>369</v>
       </c>
-      <c r="W6" s="60"/>
-    </row>
-    <row r="7" spans="1:27" ht="19" x14ac:dyDescent="0.95">
+      <c r="W6" s="59"/>
+    </row>
+    <row r="7" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C7">
         <v>2023</v>
       </c>
       <c r="D7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F7">
         <v>127150</v>
@@ -6095,52 +6091,52 @@
         <v>93</v>
       </c>
       <c r="K7" t="s">
+        <v>278</v>
+      </c>
+      <c r="M7" t="s">
+        <v>287</v>
+      </c>
+      <c r="N7" t="s">
         <v>280</v>
       </c>
-      <c r="M7" t="s">
-        <v>289</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
+        <v>288</v>
+      </c>
+      <c r="P7" t="s">
+        <v>291</v>
+      </c>
+      <c r="R7" t="s">
+        <v>291</v>
+      </c>
+      <c r="S7" t="s">
         <v>282</v>
       </c>
-      <c r="O7" t="s">
-        <v>290</v>
-      </c>
-      <c r="P7" t="s">
-        <v>293</v>
-      </c>
-      <c r="R7" t="s">
-        <v>293</v>
-      </c>
-      <c r="S7" t="s">
+      <c r="T7" s="57" t="s">
+        <v>283</v>
+      </c>
+      <c r="U7" s="57" t="s">
         <v>284</v>
       </c>
-      <c r="T7" s="58" t="s">
-        <v>285</v>
-      </c>
-      <c r="U7" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="V7" s="60">
+      <c r="V7" s="59">
         <v>2547</v>
       </c>
-      <c r="W7" s="60"/>
-    </row>
-    <row r="8" spans="1:27" ht="19" x14ac:dyDescent="0.95">
+      <c r="W7" s="59"/>
+    </row>
+    <row r="8" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C8">
         <v>2023</v>
       </c>
       <c r="D8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F8">
         <v>127150</v>
@@ -6158,52 +6154,52 @@
         <v>93</v>
       </c>
       <c r="K8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="N8" t="s">
+        <v>280</v>
+      </c>
+      <c r="O8" t="s">
+        <v>288</v>
+      </c>
+      <c r="P8" t="s">
+        <v>291</v>
+      </c>
+      <c r="R8" t="s">
+        <v>291</v>
+      </c>
+      <c r="S8" t="s">
         <v>282</v>
       </c>
-      <c r="O8" t="s">
-        <v>290</v>
-      </c>
-      <c r="P8" t="s">
-        <v>293</v>
-      </c>
-      <c r="R8" t="s">
-        <v>293</v>
-      </c>
-      <c r="S8" t="s">
+      <c r="T8" s="57" t="s">
+        <v>283</v>
+      </c>
+      <c r="U8" s="57" t="s">
         <v>284</v>
       </c>
-      <c r="T8" s="58" t="s">
-        <v>285</v>
-      </c>
-      <c r="U8" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="V8" s="60">
+      <c r="V8" s="59">
         <v>236</v>
       </c>
-      <c r="W8" s="60"/>
-    </row>
-    <row r="9" spans="1:27" ht="19" x14ac:dyDescent="0.95">
+      <c r="W8" s="59"/>
+    </row>
+    <row r="9" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C9">
         <v>2023</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F9">
         <v>127150</v>
@@ -6221,52 +6217,52 @@
         <v>93</v>
       </c>
       <c r="K9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="M9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="N9" t="s">
+        <v>280</v>
+      </c>
+      <c r="O9" t="s">
+        <v>288</v>
+      </c>
+      <c r="P9" t="s">
+        <v>291</v>
+      </c>
+      <c r="R9" t="s">
+        <v>291</v>
+      </c>
+      <c r="S9" t="s">
         <v>282</v>
       </c>
-      <c r="O9" t="s">
-        <v>290</v>
-      </c>
-      <c r="P9" t="s">
-        <v>293</v>
-      </c>
-      <c r="R9" t="s">
-        <v>293</v>
-      </c>
-      <c r="S9" t="s">
+      <c r="T9" s="57" t="s">
+        <v>283</v>
+      </c>
+      <c r="U9" s="57" t="s">
         <v>284</v>
       </c>
-      <c r="T9" s="58" t="s">
-        <v>285</v>
-      </c>
-      <c r="U9" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="V9" s="60">
+      <c r="V9" s="59">
         <v>2589</v>
       </c>
-      <c r="W9" s="60"/>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.75">
+      <c r="W9" s="59"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>129</v>
       </c>
       <c r="B10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C10">
         <v>2023</v>
       </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F10">
         <v>127150</v>
@@ -6275,10 +6271,10 @@
         <v>169</v>
       </c>
       <c r="H10" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I10" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J10" t="s">
         <v>3</v>
@@ -6290,22 +6286,22 @@
         <v>160</v>
       </c>
       <c r="N10" t="s">
+        <v>297</v>
+      </c>
+      <c r="O10" t="s">
+        <v>298</v>
+      </c>
+      <c r="P10" t="s">
         <v>299</v>
       </c>
-      <c r="O10" t="s">
+      <c r="Q10" t="s">
         <v>300</v>
-      </c>
-      <c r="P10" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>302</v>
       </c>
       <c r="R10">
         <v>208.69800000000001</v>
       </c>
       <c r="T10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U10">
         <v>15</v>
@@ -6317,21 +6313,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>129</v>
       </c>
       <c r="B11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C11">
         <v>2023</v>
       </c>
       <c r="D11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F11">
         <v>127150</v>
@@ -6340,10 +6336,10 @@
         <v>169</v>
       </c>
       <c r="H11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I11" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J11" t="s">
         <v>3</v>
@@ -6355,22 +6351,22 @@
         <v>160</v>
       </c>
       <c r="N11" t="s">
+        <v>297</v>
+      </c>
+      <c r="O11" t="s">
+        <v>298</v>
+      </c>
+      <c r="P11" t="s">
         <v>299</v>
       </c>
-      <c r="O11" t="s">
+      <c r="Q11" t="s">
         <v>300</v>
-      </c>
-      <c r="P11" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>302</v>
       </c>
       <c r="R11">
         <v>42.3384</v>
       </c>
       <c r="T11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U11">
         <v>15</v>
@@ -6382,21 +6378,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>129</v>
       </c>
       <c r="B12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C12">
         <v>2023</v>
       </c>
       <c r="D12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F12">
         <v>127150</v>
@@ -6405,10 +6401,10 @@
         <v>169</v>
       </c>
       <c r="H12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J12" t="s">
         <v>3</v>
@@ -6420,22 +6416,22 @@
         <v>160</v>
       </c>
       <c r="N12" t="s">
+        <v>297</v>
+      </c>
+      <c r="O12" t="s">
+        <v>298</v>
+      </c>
+      <c r="P12" t="s">
         <v>299</v>
       </c>
-      <c r="O12" t="s">
+      <c r="Q12" t="s">
         <v>300</v>
-      </c>
-      <c r="P12" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>302</v>
       </c>
       <c r="R12">
         <v>17.529620000000001</v>
       </c>
       <c r="T12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U12">
         <v>15</v>
@@ -6447,21 +6443,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>129</v>
       </c>
       <c r="B13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C13">
         <v>2023</v>
       </c>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F13">
         <v>127150</v>
@@ -6470,10 +6466,10 @@
         <v>169</v>
       </c>
       <c r="H13" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J13" t="s">
         <v>3</v>
@@ -6485,22 +6481,22 @@
         <v>160</v>
       </c>
       <c r="N13" t="s">
+        <v>297</v>
+      </c>
+      <c r="O13" t="s">
+        <v>298</v>
+      </c>
+      <c r="P13" t="s">
         <v>299</v>
       </c>
-      <c r="O13" t="s">
+      <c r="Q13" t="s">
         <v>300</v>
-      </c>
-      <c r="P13" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>302</v>
       </c>
       <c r="R13">
         <v>11.48574</v>
       </c>
       <c r="T13" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U13">
         <v>15</v>
@@ -6512,21 +6508,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>129</v>
       </c>
       <c r="B14" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C14">
         <v>2023</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E14" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F14">
         <v>127150</v>
@@ -6535,10 +6531,10 @@
         <v>169</v>
       </c>
       <c r="H14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I14" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J14" t="s">
         <v>3</v>
@@ -6550,22 +6546,22 @@
         <v>160</v>
       </c>
       <c r="N14" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="O14" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P14" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q14" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R14">
         <v>478.71000000000004</v>
       </c>
       <c r="T14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U14">
         <v>15</v>
@@ -6577,21 +6573,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>129</v>
       </c>
       <c r="B15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C15">
         <v>2023</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F15">
         <v>127150</v>
@@ -6600,10 +6596,10 @@
         <v>169</v>
       </c>
       <c r="H15" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J15" t="s">
         <v>3</v>
@@ -6615,22 +6611,22 @@
         <v>160</v>
       </c>
       <c r="N15" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="O15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q15" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R15">
         <v>584.97</v>
       </c>
       <c r="T15" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U15">
         <v>15</v>
@@ -6642,21 +6638,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>129</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C16">
         <v>2023</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E16" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F16">
         <v>127150</v>
@@ -6665,10 +6661,10 @@
         <v>169</v>
       </c>
       <c r="H16" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I16" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J16" t="s">
         <v>3</v>
@@ -6680,22 +6676,22 @@
         <v>160</v>
       </c>
       <c r="N16" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="O16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R16">
         <v>907.98</v>
       </c>
       <c r="T16" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U16">
         <v>15</v>
@@ -6707,21 +6703,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>129</v>
       </c>
       <c r="B17" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C17">
         <v>2023</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E17" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F17">
         <v>127150</v>
@@ -6730,10 +6726,10 @@
         <v>169</v>
       </c>
       <c r="H17" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I17" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J17" t="s">
         <v>3</v>
@@ -6745,22 +6741,22 @@
         <v>160</v>
       </c>
       <c r="N17" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="O17" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q17" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R17">
         <v>1290.6899999999998</v>
       </c>
       <c r="T17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U17">
         <v>15</v>
@@ -6772,21 +6768,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>129</v>
       </c>
       <c r="B18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C18">
         <v>2023</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F18">
         <v>127150</v>
@@ -6795,10 +6791,10 @@
         <v>169</v>
       </c>
       <c r="H18" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I18" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J18" t="s">
         <v>3</v>
@@ -6813,19 +6809,19 @@
         <v>2</v>
       </c>
       <c r="O18" t="s">
+        <v>298</v>
+      </c>
+      <c r="P18" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q18" t="s">
         <v>300</v>
-      </c>
-      <c r="P18" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>302</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="T18" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U18">
         <v>15</v>
@@ -6837,21 +6833,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>129</v>
       </c>
       <c r="B19" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C19">
         <v>2023</v>
       </c>
       <c r="D19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F19">
         <v>127150</v>
@@ -6860,10 +6856,10 @@
         <v>169</v>
       </c>
       <c r="H19" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I19" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J19" t="s">
         <v>3</v>
@@ -6878,19 +6874,19 @@
         <v>2</v>
       </c>
       <c r="O19" t="s">
+        <v>298</v>
+      </c>
+      <c r="P19" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q19" t="s">
         <v>300</v>
-      </c>
-      <c r="P19" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>302</v>
       </c>
       <c r="R19">
         <v>150</v>
       </c>
       <c r="T19" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U19">
         <v>15</v>
@@ -6902,21 +6898,21 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>129</v>
       </c>
       <c r="B20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C20">
         <v>2023</v>
       </c>
       <c r="D20" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F20">
         <v>127150</v>
@@ -6925,10 +6921,10 @@
         <v>169</v>
       </c>
       <c r="H20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J20" t="s">
         <v>3</v>
@@ -6943,19 +6939,19 @@
         <v>2</v>
       </c>
       <c r="O20" t="s">
+        <v>298</v>
+      </c>
+      <c r="P20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q20" t="s">
         <v>300</v>
-      </c>
-      <c r="P20" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>302</v>
       </c>
       <c r="R20">
         <v>200</v>
       </c>
       <c r="T20" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U20">
         <v>15</v>
@@ -6967,21 +6963,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>129</v>
       </c>
       <c r="B21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C21">
         <v>2023</v>
       </c>
       <c r="D21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E21" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F21">
         <v>127150</v>
@@ -6990,10 +6986,10 @@
         <v>169</v>
       </c>
       <c r="H21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I21" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J21" t="s">
         <v>3</v>
@@ -7008,19 +7004,19 @@
         <v>2</v>
       </c>
       <c r="O21" t="s">
+        <v>298</v>
+      </c>
+      <c r="P21" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q21" t="s">
         <v>300</v>
-      </c>
-      <c r="P21" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>302</v>
       </c>
       <c r="R21">
         <v>250</v>
       </c>
       <c r="T21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U21">
         <v>15</v>
@@ -7032,21 +7028,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>129</v>
       </c>
       <c r="B22" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C22">
         <v>2024</v>
       </c>
       <c r="D22" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E22" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F22">
         <v>127150</v>
@@ -7055,10 +7051,10 @@
         <v>169</v>
       </c>
       <c r="H22" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I22" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J22" t="s">
         <v>3</v>
@@ -7073,19 +7069,19 @@
         <v>2</v>
       </c>
       <c r="O22" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P22" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q22" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R22">
         <v>208.69800000000001</v>
       </c>
       <c r="T22" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U22">
         <v>15</v>
@@ -7097,21 +7093,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>129</v>
       </c>
       <c r="B23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C23">
         <v>2025</v>
       </c>
       <c r="D23" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E23" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F23">
         <v>127150</v>
@@ -7120,10 +7116,10 @@
         <v>169</v>
       </c>
       <c r="H23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I23" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J23" t="s">
         <v>3</v>
@@ -7138,19 +7134,19 @@
         <v>2</v>
       </c>
       <c r="O23" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P23" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q23" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R23">
         <v>42.3384</v>
       </c>
       <c r="T23" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U23">
         <v>15</v>
@@ -7162,21 +7158,21 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>129</v>
       </c>
       <c r="B24" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C24">
         <v>2026</v>
       </c>
       <c r="D24" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E24" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F24">
         <v>127150</v>
@@ -7185,10 +7181,10 @@
         <v>169</v>
       </c>
       <c r="H24" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J24" t="s">
         <v>3</v>
@@ -7203,19 +7199,19 @@
         <v>2</v>
       </c>
       <c r="O24" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P24" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q24" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R24">
         <v>17.529620000000001</v>
       </c>
       <c r="T24" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U24">
         <v>15</v>
@@ -7227,21 +7223,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>129</v>
       </c>
       <c r="B25" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C25">
         <v>2027</v>
       </c>
       <c r="D25" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E25" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F25">
         <v>127150</v>
@@ -7250,10 +7246,10 @@
         <v>169</v>
       </c>
       <c r="H25" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I25" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J25" t="s">
         <v>3</v>
@@ -7268,19 +7264,19 @@
         <v>2</v>
       </c>
       <c r="O25" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P25" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q25" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R25">
         <v>11.48574</v>
       </c>
       <c r="T25" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U25">
         <v>15</v>
@@ -7292,33 +7288,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>129</v>
       </c>
       <c r="B26" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C26">
         <v>2023</v>
       </c>
       <c r="D26" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F26">
         <v>127150</v>
       </c>
       <c r="G26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H26" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I26" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J26" t="s">
         <v>3</v>
@@ -7330,22 +7326,22 @@
         <v>160</v>
       </c>
       <c r="N26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O26" t="s">
+        <v>298</v>
+      </c>
+      <c r="P26" t="s">
         <v>299</v>
       </c>
-      <c r="O26" t="s">
+      <c r="Q26" t="s">
         <v>300</v>
-      </c>
-      <c r="P26" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>302</v>
       </c>
       <c r="R26">
         <v>208.69800000000001</v>
       </c>
       <c r="T26" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U26">
         <v>15</v>
@@ -7357,33 +7353,33 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>129</v>
       </c>
       <c r="B27" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C27">
         <v>2023</v>
       </c>
       <c r="D27" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E27" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F27">
         <v>127150</v>
       </c>
       <c r="G27" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H27" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I27" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J27" t="s">
         <v>3</v>
@@ -7395,22 +7391,22 @@
         <v>160</v>
       </c>
       <c r="N27" t="s">
+        <v>297</v>
+      </c>
+      <c r="O27" t="s">
+        <v>298</v>
+      </c>
+      <c r="P27" t="s">
         <v>299</v>
       </c>
-      <c r="O27" t="s">
+      <c r="Q27" t="s">
         <v>300</v>
-      </c>
-      <c r="P27" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>302</v>
       </c>
       <c r="R27">
         <v>42.3384</v>
       </c>
       <c r="T27" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U27">
         <v>15</v>
@@ -7422,33 +7418,33 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>129</v>
       </c>
       <c r="B28" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C28">
         <v>2023</v>
       </c>
       <c r="D28" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E28" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F28">
         <v>127150</v>
       </c>
       <c r="G28" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H28" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I28" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J28" t="s">
         <v>3</v>
@@ -7460,22 +7456,22 @@
         <v>160</v>
       </c>
       <c r="N28" t="s">
+        <v>297</v>
+      </c>
+      <c r="O28" t="s">
+        <v>298</v>
+      </c>
+      <c r="P28" t="s">
         <v>299</v>
       </c>
-      <c r="O28" t="s">
+      <c r="Q28" t="s">
         <v>300</v>
-      </c>
-      <c r="P28" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>302</v>
       </c>
       <c r="R28">
         <v>17.529620000000001</v>
       </c>
       <c r="T28" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U28">
         <v>15</v>
@@ -7487,33 +7483,33 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>129</v>
       </c>
       <c r="B29" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C29">
         <v>2023</v>
       </c>
       <c r="D29" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E29" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F29">
         <v>127150</v>
       </c>
       <c r="G29" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H29" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I29" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J29" t="s">
         <v>3</v>
@@ -7525,22 +7521,22 @@
         <v>160</v>
       </c>
       <c r="N29" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="O29" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P29" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q29" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R29">
         <v>478.71000000000004</v>
       </c>
       <c r="T29" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U29">
         <v>15</v>
@@ -7552,33 +7548,33 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>129</v>
       </c>
       <c r="B30" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C30">
         <v>2023</v>
       </c>
       <c r="D30" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E30" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F30">
         <v>127150</v>
       </c>
       <c r="G30" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H30" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I30" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J30" t="s">
         <v>3</v>
@@ -7590,22 +7586,22 @@
         <v>160</v>
       </c>
       <c r="N30" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="O30" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P30" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q30" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R30">
         <v>584.97</v>
       </c>
       <c r="T30" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U30">
         <v>15</v>
@@ -7617,33 +7613,33 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C31">
         <v>2023</v>
       </c>
       <c r="D31" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E31" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F31">
         <v>127150</v>
       </c>
       <c r="G31" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H31" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I31" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J31" t="s">
         <v>3</v>
@@ -7655,22 +7651,22 @@
         <v>160</v>
       </c>
       <c r="N31" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="O31" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P31" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q31" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R31">
         <v>907.98</v>
       </c>
       <c r="T31" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U31">
         <v>15</v>
@@ -7682,33 +7678,33 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>129</v>
       </c>
       <c r="B32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C32">
         <v>2023</v>
       </c>
       <c r="D32" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E32" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F32">
         <v>127150</v>
       </c>
       <c r="G32" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H32" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I32" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J32" t="s">
         <v>3</v>
@@ -7723,19 +7719,19 @@
         <v>2</v>
       </c>
       <c r="O32" t="s">
+        <v>298</v>
+      </c>
+      <c r="P32" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q32" t="s">
         <v>300</v>
-      </c>
-      <c r="P32" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>302</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="T32" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U32">
         <v>15</v>
@@ -7747,33 +7743,33 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>129</v>
       </c>
       <c r="B33" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C33">
         <v>2023</v>
       </c>
       <c r="D33" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F33">
         <v>127150</v>
       </c>
       <c r="G33" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H33" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J33" t="s">
         <v>3</v>
@@ -7788,19 +7784,19 @@
         <v>2</v>
       </c>
       <c r="O33" t="s">
+        <v>298</v>
+      </c>
+      <c r="P33" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q33" t="s">
         <v>300</v>
-      </c>
-      <c r="P33" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>302</v>
       </c>
       <c r="R33">
         <v>150</v>
       </c>
       <c r="T33" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U33">
         <v>15</v>
@@ -7812,33 +7808,33 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>129</v>
       </c>
       <c r="B34" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C34">
         <v>2023</v>
       </c>
       <c r="D34" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E34" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F34">
         <v>127150</v>
       </c>
       <c r="G34" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H34" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I34" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J34" t="s">
         <v>3</v>
@@ -7853,19 +7849,19 @@
         <v>2</v>
       </c>
       <c r="O34" t="s">
+        <v>298</v>
+      </c>
+      <c r="P34" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q34" t="s">
         <v>300</v>
-      </c>
-      <c r="P34" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>302</v>
       </c>
       <c r="R34">
         <v>200</v>
       </c>
       <c r="T34" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U34">
         <v>15</v>
@@ -7877,33 +7873,33 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>129</v>
       </c>
       <c r="B35" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C35">
         <v>2024</v>
       </c>
       <c r="D35" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E35" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F35">
         <v>127150</v>
       </c>
       <c r="G35" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H35" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I35" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J35" t="s">
         <v>3</v>
@@ -7918,19 +7914,19 @@
         <v>2</v>
       </c>
       <c r="O35" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P35" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q35" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R35">
         <v>208.69800000000001</v>
       </c>
       <c r="T35" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U35">
         <v>15</v>
@@ -7942,33 +7938,33 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>129</v>
       </c>
       <c r="B36" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C36">
         <v>2025</v>
       </c>
       <c r="D36" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E36" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F36">
         <v>127150</v>
       </c>
       <c r="G36" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H36" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I36" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J36" t="s">
         <v>3</v>
@@ -7983,19 +7979,19 @@
         <v>2</v>
       </c>
       <c r="O36" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P36" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q36" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R36">
         <v>42.3384</v>
       </c>
       <c r="T36" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U36">
         <v>15</v>
@@ -8007,33 +8003,33 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>129</v>
       </c>
       <c r="B37" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C37">
         <v>2026</v>
       </c>
       <c r="D37" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E37" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F37">
         <v>127150</v>
       </c>
       <c r="G37" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H37" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I37" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J37" t="s">
         <v>3</v>
@@ -8048,19 +8044,19 @@
         <v>2</v>
       </c>
       <c r="O37" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P37" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q37" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R37">
         <v>17.529620000000001</v>
       </c>
       <c r="T37" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U37">
         <v>15</v>
@@ -8079,26 +8075,26 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C252F49-FECA-4CFA-AD70-037B1BFFBBFE}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.31640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.76953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.76953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>17</v>
       </c>
@@ -8106,7 +8102,18 @@
         <v>46082</v>
       </c>
       <c r="C2" t="s">
-        <v>250</v>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>17</v>
+      </c>
+      <c r="B3" s="56">
+        <v>46126</v>
+      </c>
+      <c r="C3" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -8115,9 +8122,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8235,25 +8245,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEB43D0-560F-48CD-B064-47F998E79E6D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8275,9 +8275,16 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEB43D0-560F-48CD-B064-47F998E79E6D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/CEF and SCF formats/CEF_v17.xlsx
+++ b/CEF and SCF formats/CEF_v17.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/kibi_dtu_dk/Documents/RDBES_gits/RDBES/CEF and SCF formats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="367" documentId="13_ncr:1_{76030238-7CD0-4D36-A740-CDFD02C3FDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D97287E9-9EB9-4227-B672-5CFB57E3987B}"/>
+  <xr:revisionPtr revIDLastSave="370" documentId="13_ncr:1_{76030238-7CD0-4D36-A740-CDFD02C3FDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E7F5937-2C51-4DBA-95EF-3E5E25F7EB19}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3BA46FC-17EC-4006-828F-4F15940585FB}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="308">
   <si>
     <t>Version</t>
   </si>
@@ -1131,6 +1131,9 @@
   </si>
   <si>
     <t>Updated accepted codes for EN.variableType</t>
+  </si>
+  <si>
+    <t>Minor updates are mark with yellow</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1250,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1263,6 +1266,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1375,7 +1384,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1507,13 +1516,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1891,6 +1904,9 @@
         <v>17</v>
       </c>
       <c r="D2" s="1"/>
+      <c r="E2" s="59" t="s">
+        <v>307</v>
+      </c>
       <c r="I2" s="15"/>
     </row>
     <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5591,13 +5607,13 @@
       <c r="G16" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="H16" s="55" t="s">
+      <c r="H16" s="60" t="s">
         <v>304</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="61" t="s">
         <v>305</v>
       </c>
       <c r="K16" s="7"/>
@@ -5769,7 +5785,7 @@
       <c r="K2" t="s">
         <v>278</v>
       </c>
-      <c r="L2" s="57"/>
+      <c r="L2" s="56"/>
       <c r="M2" s="11" t="s">
         <v>279</v>
       </c>
@@ -5779,26 +5795,26 @@
       <c r="O2" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
       <c r="S2" t="s">
         <v>282</v>
       </c>
-      <c r="T2" s="57" t="s">
+      <c r="T2" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="U2" s="57" t="s">
+      <c r="U2" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="V2" s="58">
+      <c r="V2" s="57">
         <v>377</v>
       </c>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
-      <c r="Y2" s="57"/>
-      <c r="Z2" s="58"/>
-      <c r="AA2" s="57"/>
+      <c r="W2" s="57"/>
+      <c r="X2" s="57"/>
+      <c r="Y2" s="56"/>
+      <c r="Z2" s="57"/>
+      <c r="AA2" s="56"/>
     </row>
     <row r="3" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -5847,20 +5863,20 @@
       <c r="S3" t="s">
         <v>289</v>
       </c>
-      <c r="T3" s="57" t="s">
+      <c r="T3" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="U3" s="57" t="s">
+      <c r="U3" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="V3" s="58">
+      <c r="V3" s="57">
         <v>15</v>
       </c>
-      <c r="W3" s="58"/>
-      <c r="X3" s="58"/>
-      <c r="Y3" s="57"/>
-      <c r="Z3" s="58"/>
-      <c r="AA3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="56"/>
+      <c r="Z3" s="57"/>
+      <c r="AA3" s="56"/>
     </row>
     <row r="4" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -5914,22 +5930,22 @@
       <c r="S4" t="s">
         <v>282</v>
       </c>
-      <c r="T4" s="57" t="s">
+      <c r="T4" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="U4" s="57" t="s">
+      <c r="U4" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="V4" s="59">
+      <c r="V4" s="58">
         <v>250</v>
       </c>
-      <c r="X4" s="59" t="s">
+      <c r="X4" s="58" t="s">
         <v>292</v>
       </c>
-      <c r="Y4" s="59">
+      <c r="Y4" s="58">
         <v>15</v>
       </c>
-      <c r="Z4" s="59">
+      <c r="Z4" s="58">
         <v>15</v>
       </c>
     </row>
@@ -5985,16 +6001,16 @@
       <c r="S5" t="s">
         <v>282</v>
       </c>
-      <c r="T5" s="57" t="s">
+      <c r="T5" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="U5" s="57" t="s">
+      <c r="U5" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="V5" s="59">
+      <c r="V5" s="58">
         <v>523</v>
       </c>
-      <c r="W5" s="59"/>
+      <c r="W5" s="58"/>
     </row>
     <row r="6" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -6048,16 +6064,16 @@
       <c r="S6" t="s">
         <v>282</v>
       </c>
-      <c r="T6" s="57" t="s">
+      <c r="T6" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="U6" s="57" t="s">
+      <c r="U6" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="V6" s="59">
+      <c r="V6" s="58">
         <v>369</v>
       </c>
-      <c r="W6" s="59"/>
+      <c r="W6" s="58"/>
     </row>
     <row r="7" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -6111,16 +6127,16 @@
       <c r="S7" t="s">
         <v>282</v>
       </c>
-      <c r="T7" s="57" t="s">
+      <c r="T7" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="U7" s="57" t="s">
+      <c r="U7" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="V7" s="59">
+      <c r="V7" s="58">
         <v>2547</v>
       </c>
-      <c r="W7" s="59"/>
+      <c r="W7" s="58"/>
     </row>
     <row r="8" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -6174,16 +6190,16 @@
       <c r="S8" t="s">
         <v>282</v>
       </c>
-      <c r="T8" s="57" t="s">
+      <c r="T8" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="U8" s="57" t="s">
+      <c r="U8" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="V8" s="59">
+      <c r="V8" s="58">
         <v>236</v>
       </c>
-      <c r="W8" s="59"/>
+      <c r="W8" s="58"/>
     </row>
     <row r="9" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -6237,16 +6253,16 @@
       <c r="S9" t="s">
         <v>282</v>
       </c>
-      <c r="T9" s="57" t="s">
+      <c r="T9" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="U9" s="57" t="s">
+      <c r="U9" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="V9" s="59">
+      <c r="V9" s="58">
         <v>2589</v>
       </c>
-      <c r="W9" s="59"/>
+      <c r="W9" s="58"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -8098,7 +8114,7 @@
       <c r="A2">
         <v>17</v>
       </c>
-      <c r="B2" s="56">
+      <c r="B2" s="55">
         <v>46082</v>
       </c>
       <c r="C2" t="s">
@@ -8109,7 +8125,7 @@
       <c r="A3">
         <v>17</v>
       </c>
-      <c r="B3" s="56">
+      <c r="B3" s="55">
         <v>46126</v>
       </c>
       <c r="C3" t="s">
@@ -8122,12 +8138,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8245,15 +8258,25 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEB43D0-560F-48CD-B064-47F998E79E6D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8275,16 +8298,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEB43D0-560F-48CD-B064-47F998E79E6D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/CEF and SCF formats/CEF_v17.xlsx
+++ b/CEF and SCF formats/CEF_v17.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/kibi_dtu_dk/Documents/RDBES_gits/RDBES/CEF and SCF formats/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Development\Rstudio\D1SCI\VISBIO\RDBES\CEF and SCF formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="370" documentId="13_ncr:1_{76030238-7CD0-4D36-A740-CDFD02C3FDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E7F5937-2C51-4DBA-95EF-3E5E25F7EB19}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80A4342-1631-4727-9251-CDD4AABAEBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3BA46FC-17EC-4006-828F-4F15940585FB}"/>
+    <workbookView xWindow="-38520" yWindow="-3105" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{C3BA46FC-17EC-4006-828F-4F15940585FB}"/>
   </bookViews>
   <sheets>
     <sheet name="CEF" sheetId="1" r:id="rId1"/>
@@ -337,9 +337,6 @@
     <t>Same defintion as in RDBES CL. ICES statistical rectangle (e.g. 41G9), mandatory for FAO area 27. (Use ‘-9’ if unknown or if not fishing in ICES area)</t>
   </si>
   <si>
-    <t xml:space="preserve">Same defintion as in RDBES CL. Source of the statistical rectangle. Report e.g. "RepLogbook" if the statistical rectangle is reported directly in logbook, "EstHarbLoc" if it is estimated based on harbour location. </t>
-  </si>
-  <si>
     <t>Metier6_FishingActivity</t>
   </si>
   <si>
@@ -866,10 +863,6 @@
 Only a single value should be accepted in seasonValue. </t>
   </si>
   <si>
-    <t>This specifies whether the total is expressed as days at sea (das), KiloWatt days (kWd), Fishing days (fd), Number of Vessels (NoV), FishingHours (hf), Number of fishing events (fe),  Kilograms per vessel per hour (kg/vessel/h), Hook Days (hd)
-The variableType should follow what is requested  through the data call.</t>
-  </si>
-  <si>
     <t>IC_FleetName, GearType, Metier5_FishingActivity &amp; Metier6_FishingActivity</t>
   </si>
   <si>
@@ -1134,6 +1127,13 @@
   </si>
   <si>
     <t>Minor updates are mark with yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same defintion as in RDBES CL. Source of the statistical rectangle. Report e.g. "Logb" if the statistical rectangle is reported directly in logbook, "HarbLoc" if it is estimated based on harbour location. </t>
+  </si>
+  <si>
+    <t>This specifies whether the total is expressed as days at sea (das), KiloWatt days at sea  (kWd-at-sea), KiloWatt Fishing days (kWd-fishing), Fishing days (fd), Number of Vessels (NoV), FishingHours (hf), Number of fishing events (fe),  Kilograms per vessel per hour (kg/vessel/h), Hook Days (hd)
+The variableType should follow what is requested  through the data call.</t>
   </si>
 </sst>
 </file>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="59" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="I2" s="15"/>
     </row>
@@ -1918,7 +1918,7 @@
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="30"/>
       <c r="B4" s="45" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="31"/>
@@ -1938,27 +1938,27 @@
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="33"/>
       <c r="B6" s="36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C6" s="36" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="34"/>
       <c r="E6" s="36" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F6" s="36" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="35"/>
       <c r="J6" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>14</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="D17" s="34"/>
       <c r="E17" s="34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F17" s="34" t="s">
         <v>2</v>
@@ -2347,7 +2347,7 @@
         <v>2</v>
       </c>
       <c r="M19" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N19" t="s">
         <v>2</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G24" s="35"/>
       <c r="J24" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K24" t="s">
         <v>2</v>
@@ -2483,7 +2483,7 @@
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="33"/>
       <c r="B25" s="34" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C25" s="34" t="s">
         <v>2</v>
@@ -2747,12 +2747,12 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>39</v>
@@ -2771,10 +2771,10 @@
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>44</v>
@@ -2783,7 +2783,7 @@
         <v>63</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>45</v>
@@ -2808,10 +2808,10 @@
         <v>48</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -2834,7 +2834,7 @@
         <v>52</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>65</v>
@@ -2844,7 +2844,7 @@
         <v>53</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -2867,17 +2867,17 @@
         <v>52</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>68</v>
       </c>
       <c r="I5" s="6"/>
       <c r="K5" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -2903,15 +2903,15 @@
         <v>69</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -2934,18 +2934,18 @@
         <v>52</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I7" s="24"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -2968,7 +2968,7 @@
         <v>52</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>71</v>
@@ -2978,7 +2978,7 @@
         <v>55</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
@@ -3001,20 +3001,20 @@
         <v>52</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>73</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -3034,20 +3034,20 @@
         <v>52</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="144" x14ac:dyDescent="0.3">
@@ -3067,17 +3067,17 @@
         <v>52</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I11" s="20"/>
       <c r="K11" s="7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -3097,19 +3097,19 @@
         <v>52</v>
       </c>
       <c r="G12" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="I12" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="H12" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>93</v>
-      </c>
       <c r="K12" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="72" x14ac:dyDescent="0.3">
@@ -3129,17 +3129,17 @@
         <v>52</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I13" s="6"/>
       <c r="K13" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -3159,17 +3159,17 @@
         <v>52</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I14" s="24"/>
       <c r="K14" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="72" x14ac:dyDescent="0.3">
@@ -3189,17 +3189,17 @@
         <v>52</v>
       </c>
       <c r="G15" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="I15" s="6"/>
       <c r="K15" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
@@ -3219,18 +3219,18 @@
         <v>52</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
       <c r="K16" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="144" x14ac:dyDescent="0.3">
@@ -3250,16 +3250,16 @@
         <v>52</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="185.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3279,10 +3279,10 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="K18" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="185.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3302,10 +3302,10 @@
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="K19" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
@@ -3328,10 +3328,10 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="K20" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
@@ -3339,7 +3339,7 @@
         <v>51</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>47</v>
@@ -3351,20 +3351,20 @@
         <v>52</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J21" s="14"/>
       <c r="K21" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L21" s="29" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="28.8" x14ac:dyDescent="0.2">
@@ -3384,20 +3384,20 @@
         <v>52</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J22" s="19"/>
       <c r="K22" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
@@ -3414,20 +3414,20 @@
         <v>52</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
@@ -3441,16 +3441,16 @@
         <v>2</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="K24" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -3470,7 +3470,7 @@
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
       <c r="K25" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
@@ -3487,20 +3487,20 @@
         <v>52</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J26" s="14"/>
       <c r="K26" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="L26" s="7" t="s">
         <v>236</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
@@ -3518,10 +3518,10 @@
       </c>
       <c r="G27" s="7"/>
       <c r="K27" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
@@ -3539,10 +3539,10 @@
       </c>
       <c r="G28" s="7"/>
       <c r="K28" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -3590,7 +3590,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3606,7 +3606,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>60</v>
@@ -3630,13 +3630,13 @@
         <v>62</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J2" s="10" t="s">
         <v>63</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L2" s="10" t="s">
         <v>45</v>
@@ -3653,18 +3653,18 @@
         <v>2</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J3" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>149</v>
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="7" t="s">
@@ -3702,7 +3702,7 @@
         <v>66</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L4" s="7"/>
     </row>
@@ -3733,10 +3733,10 @@
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L5" s="7"/>
     </row>
@@ -3763,14 +3763,14 @@
         <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L6" s="7"/>
     </row>
@@ -3794,16 +3794,16 @@
         <v>52</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L7" s="7"/>
     </row>
@@ -3837,7 +3837,7 @@
         <v>72</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L8" s="7"/>
     </row>
@@ -3861,19 +3861,19 @@
         <v>52</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>73</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J9" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>189</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>190</v>
       </c>
       <c r="L9" s="7"/>
     </row>
@@ -3898,10 +3898,10 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L10" s="7"/>
     </row>
@@ -3922,19 +3922,19 @@
         <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L11" s="7"/>
     </row>
@@ -3953,19 +3953,19 @@
         <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L12" s="7"/>
     </row>
@@ -3974,7 +3974,7 @@
         <v>51</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>54</v>
@@ -3987,7 +3987,7 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -4008,10 +4008,10 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L14" s="7"/>
     </row>
@@ -4033,19 +4033,19 @@
         <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L15" s="5"/>
     </row>
@@ -4067,19 +4067,19 @@
         <v>52</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H16" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="H16" s="47" t="s">
-        <v>142</v>
-      </c>
       <c r="I16" s="47" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L16" s="5"/>
     </row>
@@ -4100,19 +4100,19 @@
         <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I17" s="48" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L17" s="7"/>
     </row>
@@ -4131,19 +4131,19 @@
         <v>52</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L18" s="7"/>
     </row>
@@ -4162,19 +4162,19 @@
         <v>52</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J19" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="K19" s="7" t="s">
         <v>215</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>216</v>
       </c>
       <c r="L19" s="7"/>
     </row>
@@ -4193,7 +4193,7 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -4214,7 +4214,7 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -4234,19 +4234,19 @@
         <v>52</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I22" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J22" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="J22" s="7" t="s">
-        <v>239</v>
-      </c>
       <c r="K22" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L22" s="7"/>
     </row>
@@ -4268,7 +4268,7 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -4291,10 +4291,10 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L24" s="7"/>
     </row>
@@ -4316,7 +4316,7 @@
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
       <c r="J25" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -4395,7 +4395,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -4432,13 +4432,13 @@
         <v>62</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>63</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K5" s="10" t="s">
         <v>45</v>
@@ -4457,18 +4457,18 @@
         <v>2</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>131</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>132</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7" t="s">
@@ -4503,7 +4503,7 @@
         <v>66</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="27"/>
@@ -4532,10 +4532,10 @@
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="27"/>
@@ -4560,14 +4560,14 @@
         <v>69</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H9" s="23"/>
       <c r="I9" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>78</v>
@@ -4591,17 +4591,17 @@
         <v>52</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H10" s="24"/>
       <c r="I10" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="27"/>
@@ -4633,7 +4633,7 @@
         <v>72</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K11" s="6"/>
       <c r="L11" s="27"/>
@@ -4655,19 +4655,19 @@
         <v>52</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>73</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="27"/>
@@ -4689,19 +4689,19 @@
         <v>52</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J13" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="27"/>
@@ -4723,17 +4723,17 @@
         <v>52</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H14" s="20"/>
       <c r="I14" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="27"/>
@@ -4753,19 +4753,19 @@
         <v>52</v>
       </c>
       <c r="F15" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="H15" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="H15" s="24" t="s">
-        <v>93</v>
-      </c>
       <c r="I15" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K15" s="6"/>
       <c r="L15" s="27"/>
@@ -4787,17 +4787,17 @@
         <v>52</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="54" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="27"/>
@@ -4822,14 +4822,14 @@
         <v>79</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H17" s="24"/>
       <c r="I17" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="27"/>
@@ -4851,7 +4851,7 @@
         <v>52</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>82</v>
@@ -4861,7 +4861,7 @@
         <v>83</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="27"/>
@@ -4883,19 +4883,19 @@
         <v>52</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H19" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="27"/>
@@ -4917,17 +4917,17 @@
         <v>52</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K20" s="6"/>
       <c r="L20" s="27"/>
@@ -4949,14 +4949,14 @@
         <v>52</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
@@ -4979,15 +4979,15 @@
         <v>52</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K22" s="6"/>
       <c r="L22" s="27"/>
@@ -4997,7 +4997,7 @@
         <v>51</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>47</v>
@@ -5009,19 +5009,19 @@
         <v>52</v>
       </c>
       <c r="F23" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K23" s="7"/>
     </row>
@@ -5042,19 +5042,19 @@
         <v>52</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K24" s="6"/>
       <c r="L24" s="27"/>
@@ -5074,19 +5074,19 @@
         <v>52</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H25" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K25" s="27"/>
       <c r="L25" s="27"/>
@@ -5103,13 +5103,13 @@
         <v>2</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="27"/>
       <c r="H26" s="27"/>
       <c r="I26" s="27" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J26" s="27"/>
       <c r="K26" s="27"/>
@@ -5141,7 +5141,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F1" s="7"/>
       <c r="I1" s="7"/>
@@ -5170,13 +5170,13 @@
         <v>62</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>63</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>45</v>
@@ -5194,18 +5194,18 @@
         <v>2</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>134</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>135</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7" t="s">
@@ -5240,7 +5240,7 @@
         <v>66</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K4" s="7"/>
     </row>
@@ -5268,10 +5268,10 @@
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K5" s="7"/>
     </row>
@@ -5295,17 +5295,17 @@
         <v>69</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H6" s="23"/>
       <c r="I6" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -5325,19 +5325,19 @@
         <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J7" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K7" s="7"/>
     </row>
@@ -5358,17 +5358,17 @@
         <v>52</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H8" s="20"/>
       <c r="I8" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K8" s="7"/>
     </row>
@@ -5389,19 +5389,19 @@
         <v>52</v>
       </c>
       <c r="F9" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="G9" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>93</v>
-      </c>
       <c r="I9" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K9" s="7"/>
     </row>
@@ -5422,16 +5422,16 @@
         <v>52</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K10" s="7"/>
     </row>
@@ -5455,14 +5455,14 @@
         <v>79</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H11" s="24"/>
       <c r="I11" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K11" s="7"/>
     </row>
@@ -5483,16 +5483,16 @@
         <v>52</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="I12" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>87</v>
-      </c>
       <c r="J12" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K12" s="7"/>
     </row>
@@ -5513,14 +5513,14 @@
         <v>52</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J13" s="46"/>
       <c r="K13" s="7"/>
@@ -5542,12 +5542,12 @@
         <v>52</v>
       </c>
       <c r="F14" s="50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="14"/>
       <c r="I14" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J14" s="28"/>
       <c r="K14" s="7"/>
@@ -5557,7 +5557,7 @@
         <v>51</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>47</v>
@@ -5569,23 +5569,23 @@
         <v>52</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:13" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>51</v>
       </c>
@@ -5602,19 +5602,19 @@
         <v>52</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H16" s="60" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>234</v>
+        <v>307</v>
       </c>
       <c r="J16" s="61" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="K16" s="7"/>
     </row>
@@ -5630,13 +5630,13 @@
         <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F17" s="27"/>
       <c r="G17" s="27"/>
       <c r="H17" s="27"/>
       <c r="I17" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="27"/>
@@ -5657,7 +5657,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D1" s="1"/>
     </row>
@@ -5688,7 +5688,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -5718,7 +5718,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -5748,7 +5748,7 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="18" x14ac:dyDescent="0.35">
@@ -5756,56 +5756,56 @@
         <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C2">
         <v>2023</v>
       </c>
       <c r="D2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F2">
         <v>127150</v>
       </c>
       <c r="G2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L2" s="56"/>
       <c r="M2" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="N2" t="s">
+        <v>278</v>
+      </c>
+      <c r="O2" s="11" t="s">
         <v>279</v>
-      </c>
-      <c r="N2" t="s">
-        <v>280</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>281</v>
       </c>
       <c r="P2" s="56"/>
       <c r="Q2" s="56"/>
       <c r="R2" s="56"/>
       <c r="S2" t="s">
+        <v>280</v>
+      </c>
+      <c r="T2" s="56" t="s">
+        <v>281</v>
+      </c>
+      <c r="U2" s="56" t="s">
         <v>282</v>
-      </c>
-      <c r="T2" s="56" t="s">
-        <v>283</v>
-      </c>
-      <c r="U2" s="56" t="s">
-        <v>284</v>
       </c>
       <c r="V2" s="57">
         <v>377</v>
@@ -5821,53 +5821,53 @@
         <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C3">
         <v>2023</v>
       </c>
       <c r="D3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F3">
         <v>127150</v>
       </c>
       <c r="G3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I3">
         <v>2023</v>
       </c>
       <c r="J3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s">
+        <v>284</v>
+      </c>
+      <c r="M3" t="s">
+        <v>285</v>
+      </c>
+      <c r="N3" t="s">
+        <v>278</v>
+      </c>
+      <c r="O3" t="s">
         <v>286</v>
-      </c>
-      <c r="M3" t="s">
-        <v>287</v>
-      </c>
-      <c r="N3" t="s">
-        <v>280</v>
-      </c>
-      <c r="O3" t="s">
-        <v>288</v>
       </c>
       <c r="P3" s="1"/>
       <c r="S3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="T3" s="56" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="U3" s="56" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="V3" s="57">
         <v>15</v>
@@ -5883,64 +5883,64 @@
         <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C4">
         <v>2023</v>
       </c>
       <c r="D4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F4">
         <v>127150</v>
       </c>
       <c r="G4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I4">
         <v>2023</v>
       </c>
       <c r="J4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="N4" t="s">
+        <v>278</v>
+      </c>
+      <c r="O4" t="s">
+        <v>286</v>
+      </c>
+      <c r="P4" t="s">
+        <v>289</v>
+      </c>
+      <c r="R4" t="s">
+        <v>289</v>
+      </c>
+      <c r="S4" t="s">
         <v>280</v>
       </c>
-      <c r="O4" t="s">
-        <v>288</v>
-      </c>
-      <c r="P4" t="s">
-        <v>291</v>
-      </c>
-      <c r="R4" t="s">
-        <v>291</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="T4" s="56" t="s">
+        <v>281</v>
+      </c>
+      <c r="U4" s="56" t="s">
         <v>282</v>
-      </c>
-      <c r="T4" s="56" t="s">
-        <v>283</v>
-      </c>
-      <c r="U4" s="56" t="s">
-        <v>284</v>
       </c>
       <c r="V4" s="58">
         <v>250</v>
       </c>
       <c r="X4" s="58" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="Y4" s="58">
         <v>15</v>
@@ -5954,58 +5954,58 @@
         <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C5">
         <v>2023</v>
       </c>
       <c r="D5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F5">
         <v>127150</v>
       </c>
       <c r="G5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I5">
         <v>2023</v>
       </c>
       <c r="J5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s">
+        <v>284</v>
+      </c>
+      <c r="M5" t="s">
+        <v>285</v>
+      </c>
+      <c r="N5" t="s">
+        <v>278</v>
+      </c>
+      <c r="O5" t="s">
         <v>286</v>
       </c>
-      <c r="M5" t="s">
-        <v>287</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="P5" t="s">
+        <v>289</v>
+      </c>
+      <c r="R5" t="s">
+        <v>289</v>
+      </c>
+      <c r="S5" t="s">
         <v>280</v>
       </c>
-      <c r="O5" t="s">
-        <v>288</v>
-      </c>
-      <c r="P5" t="s">
-        <v>291</v>
-      </c>
-      <c r="R5" t="s">
-        <v>291</v>
-      </c>
-      <c r="S5" t="s">
+      <c r="T5" s="56" t="s">
+        <v>281</v>
+      </c>
+      <c r="U5" s="56" t="s">
         <v>282</v>
-      </c>
-      <c r="T5" s="56" t="s">
-        <v>283</v>
-      </c>
-      <c r="U5" s="56" t="s">
-        <v>284</v>
       </c>
       <c r="V5" s="58">
         <v>523</v>
@@ -6017,58 +6017,58 @@
         <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C6">
         <v>2023</v>
       </c>
       <c r="D6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F6">
         <v>127150</v>
       </c>
       <c r="G6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I6">
         <v>2023</v>
       </c>
       <c r="J6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="N6" t="s">
+        <v>278</v>
+      </c>
+      <c r="O6" t="s">
+        <v>286</v>
+      </c>
+      <c r="P6" t="s">
+        <v>289</v>
+      </c>
+      <c r="R6" t="s">
+        <v>289</v>
+      </c>
+      <c r="S6" t="s">
         <v>280</v>
       </c>
-      <c r="O6" t="s">
-        <v>288</v>
-      </c>
-      <c r="P6" t="s">
-        <v>291</v>
-      </c>
-      <c r="R6" t="s">
-        <v>291</v>
-      </c>
-      <c r="S6" t="s">
+      <c r="T6" s="56" t="s">
+        <v>281</v>
+      </c>
+      <c r="U6" s="56" t="s">
         <v>282</v>
-      </c>
-      <c r="T6" s="56" t="s">
-        <v>283</v>
-      </c>
-      <c r="U6" s="56" t="s">
-        <v>284</v>
       </c>
       <c r="V6" s="58">
         <v>369</v>
@@ -6080,58 +6080,58 @@
         <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C7">
         <v>2023</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F7">
         <v>127150</v>
       </c>
       <c r="G7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I7">
         <v>2023</v>
       </c>
       <c r="J7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K7" t="s">
+        <v>276</v>
+      </c>
+      <c r="M7" t="s">
+        <v>285</v>
+      </c>
+      <c r="N7" t="s">
         <v>278</v>
       </c>
-      <c r="M7" t="s">
-        <v>287</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
+        <v>286</v>
+      </c>
+      <c r="P7" t="s">
+        <v>289</v>
+      </c>
+      <c r="R7" t="s">
+        <v>289</v>
+      </c>
+      <c r="S7" t="s">
         <v>280</v>
       </c>
-      <c r="O7" t="s">
-        <v>288</v>
-      </c>
-      <c r="P7" t="s">
-        <v>291</v>
-      </c>
-      <c r="R7" t="s">
-        <v>291</v>
-      </c>
-      <c r="S7" t="s">
+      <c r="T7" s="56" t="s">
+        <v>281</v>
+      </c>
+      <c r="U7" s="56" t="s">
         <v>282</v>
-      </c>
-      <c r="T7" s="56" t="s">
-        <v>283</v>
-      </c>
-      <c r="U7" s="56" t="s">
-        <v>284</v>
       </c>
       <c r="V7" s="58">
         <v>2547</v>
@@ -6143,58 +6143,58 @@
         <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C8">
         <v>2023</v>
       </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F8">
         <v>127150</v>
       </c>
       <c r="G8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I8">
         <v>2023</v>
       </c>
       <c r="J8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="N8" t="s">
+        <v>278</v>
+      </c>
+      <c r="O8" t="s">
+        <v>286</v>
+      </c>
+      <c r="P8" t="s">
+        <v>289</v>
+      </c>
+      <c r="R8" t="s">
+        <v>289</v>
+      </c>
+      <c r="S8" t="s">
         <v>280</v>
       </c>
-      <c r="O8" t="s">
-        <v>288</v>
-      </c>
-      <c r="P8" t="s">
-        <v>291</v>
-      </c>
-      <c r="R8" t="s">
-        <v>291</v>
-      </c>
-      <c r="S8" t="s">
+      <c r="T8" s="56" t="s">
+        <v>281</v>
+      </c>
+      <c r="U8" s="56" t="s">
         <v>282</v>
-      </c>
-      <c r="T8" s="56" t="s">
-        <v>283</v>
-      </c>
-      <c r="U8" s="56" t="s">
-        <v>284</v>
       </c>
       <c r="V8" s="58">
         <v>236</v>
@@ -6206,58 +6206,58 @@
         <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C9">
         <v>2023</v>
       </c>
       <c r="D9" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F9">
         <v>127150</v>
       </c>
       <c r="G9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I9">
         <v>2023</v>
       </c>
       <c r="J9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="N9" t="s">
+        <v>278</v>
+      </c>
+      <c r="O9" t="s">
+        <v>286</v>
+      </c>
+      <c r="P9" t="s">
+        <v>289</v>
+      </c>
+      <c r="R9" t="s">
+        <v>289</v>
+      </c>
+      <c r="S9" t="s">
         <v>280</v>
       </c>
-      <c r="O9" t="s">
-        <v>288</v>
-      </c>
-      <c r="P9" t="s">
-        <v>291</v>
-      </c>
-      <c r="R9" t="s">
-        <v>291</v>
-      </c>
-      <c r="S9" t="s">
+      <c r="T9" s="56" t="s">
+        <v>281</v>
+      </c>
+      <c r="U9" s="56" t="s">
         <v>282</v>
-      </c>
-      <c r="T9" s="56" t="s">
-        <v>283</v>
-      </c>
-      <c r="U9" s="56" t="s">
-        <v>284</v>
       </c>
       <c r="V9" s="58">
         <v>2589</v>
@@ -6266,31 +6266,31 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C10">
         <v>2023</v>
       </c>
       <c r="D10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F10">
         <v>127150</v>
       </c>
       <c r="G10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I10" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J10" t="s">
         <v>3</v>
@@ -6299,25 +6299,25 @@
         <v>2</v>
       </c>
       <c r="M10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N10" t="s">
+        <v>295</v>
+      </c>
+      <c r="O10" t="s">
+        <v>296</v>
+      </c>
+      <c r="P10" t="s">
         <v>297</v>
       </c>
-      <c r="O10" t="s">
+      <c r="Q10" t="s">
         <v>298</v>
-      </c>
-      <c r="P10" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>300</v>
       </c>
       <c r="R10">
         <v>208.69800000000001</v>
       </c>
       <c r="T10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U10">
         <v>15</v>
@@ -6331,31 +6331,31 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C11">
         <v>2023</v>
       </c>
       <c r="D11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F11">
         <v>127150</v>
       </c>
       <c r="G11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J11" t="s">
         <v>3</v>
@@ -6364,25 +6364,25 @@
         <v>3</v>
       </c>
       <c r="M11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N11" t="s">
+        <v>295</v>
+      </c>
+      <c r="O11" t="s">
+        <v>296</v>
+      </c>
+      <c r="P11" t="s">
         <v>297</v>
       </c>
-      <c r="O11" t="s">
+      <c r="Q11" t="s">
         <v>298</v>
-      </c>
-      <c r="P11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>300</v>
       </c>
       <c r="R11">
         <v>42.3384</v>
       </c>
       <c r="T11" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U11">
         <v>15</v>
@@ -6396,31 +6396,31 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C12">
         <v>2023</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F12">
         <v>127150</v>
       </c>
       <c r="G12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J12" t="s">
         <v>3</v>
@@ -6429,25 +6429,25 @@
         <v>4</v>
       </c>
       <c r="M12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N12" t="s">
+        <v>295</v>
+      </c>
+      <c r="O12" t="s">
+        <v>296</v>
+      </c>
+      <c r="P12" t="s">
         <v>297</v>
       </c>
-      <c r="O12" t="s">
+      <c r="Q12" t="s">
         <v>298</v>
-      </c>
-      <c r="P12" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>300</v>
       </c>
       <c r="R12">
         <v>17.529620000000001</v>
       </c>
       <c r="T12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U12">
         <v>15</v>
@@ -6461,31 +6461,31 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C13">
         <v>2023</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F13">
         <v>127150</v>
       </c>
       <c r="G13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H13" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I13" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J13" t="s">
         <v>3</v>
@@ -6494,25 +6494,25 @@
         <v>5</v>
       </c>
       <c r="M13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s">
+        <v>295</v>
+      </c>
+      <c r="O13" t="s">
+        <v>296</v>
+      </c>
+      <c r="P13" t="s">
         <v>297</v>
       </c>
-      <c r="O13" t="s">
+      <c r="Q13" t="s">
         <v>298</v>
-      </c>
-      <c r="P13" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>300</v>
       </c>
       <c r="R13">
         <v>11.48574</v>
       </c>
       <c r="T13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U13">
         <v>15</v>
@@ -6526,31 +6526,31 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C14">
         <v>2023</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E14" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F14">
         <v>127150</v>
       </c>
       <c r="G14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H14" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J14" t="s">
         <v>3</v>
@@ -6559,25 +6559,25 @@
         <v>2</v>
       </c>
       <c r="M14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N14" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O14" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P14" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R14">
         <v>478.71000000000004</v>
       </c>
       <c r="T14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U14">
         <v>15</v>
@@ -6591,31 +6591,31 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C15">
         <v>2023</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F15">
         <v>127150</v>
       </c>
       <c r="G15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H15" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I15" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J15" t="s">
         <v>3</v>
@@ -6624,25 +6624,25 @@
         <v>3</v>
       </c>
       <c r="M15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N15" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O15" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P15" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q15" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R15">
         <v>584.97</v>
       </c>
       <c r="T15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U15">
         <v>15</v>
@@ -6656,31 +6656,31 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C16">
         <v>2023</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F16">
         <v>127150</v>
       </c>
       <c r="G16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H16" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I16" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J16" t="s">
         <v>3</v>
@@ -6689,25 +6689,25 @@
         <v>4</v>
       </c>
       <c r="M16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N16" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P16" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q16" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R16">
         <v>907.98</v>
       </c>
       <c r="T16" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U16">
         <v>15</v>
@@ -6721,31 +6721,31 @@
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B17" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C17">
         <v>2023</v>
       </c>
       <c r="D17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E17" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F17">
         <v>127150</v>
       </c>
       <c r="G17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H17" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I17" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J17" t="s">
         <v>3</v>
@@ -6754,25 +6754,25 @@
         <v>5</v>
       </c>
       <c r="M17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N17" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O17" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P17" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R17">
         <v>1290.6899999999998</v>
       </c>
       <c r="T17" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U17">
         <v>15</v>
@@ -6786,31 +6786,31 @@
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B18" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C18">
         <v>2023</v>
       </c>
       <c r="D18" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F18">
         <v>127150</v>
       </c>
       <c r="G18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I18" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J18" t="s">
         <v>3</v>
@@ -6819,25 +6819,25 @@
         <v>2</v>
       </c>
       <c r="M18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N18" t="s">
         <v>2</v>
       </c>
       <c r="O18" t="s">
+        <v>296</v>
+      </c>
+      <c r="P18" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q18" t="s">
         <v>298</v>
-      </c>
-      <c r="P18" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>300</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="T18" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U18">
         <v>15</v>
@@ -6851,31 +6851,31 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C19">
         <v>2023</v>
       </c>
       <c r="D19" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E19" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F19">
         <v>127150</v>
       </c>
       <c r="G19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H19" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I19" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J19" t="s">
         <v>3</v>
@@ -6884,25 +6884,25 @@
         <v>3</v>
       </c>
       <c r="M19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N19" t="s">
         <v>2</v>
       </c>
       <c r="O19" t="s">
+        <v>296</v>
+      </c>
+      <c r="P19" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q19" t="s">
         <v>298</v>
-      </c>
-      <c r="P19" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>300</v>
       </c>
       <c r="R19">
         <v>150</v>
       </c>
       <c r="T19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U19">
         <v>15</v>
@@ -6916,31 +6916,31 @@
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B20" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C20">
         <v>2023</v>
       </c>
       <c r="D20" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F20">
         <v>127150</v>
       </c>
       <c r="G20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H20" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I20" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J20" t="s">
         <v>3</v>
@@ -6949,25 +6949,25 @@
         <v>4</v>
       </c>
       <c r="M20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N20" t="s">
         <v>2</v>
       </c>
       <c r="O20" t="s">
+        <v>296</v>
+      </c>
+      <c r="P20" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q20" t="s">
         <v>298</v>
-      </c>
-      <c r="P20" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>300</v>
       </c>
       <c r="R20">
         <v>200</v>
       </c>
       <c r="T20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U20">
         <v>15</v>
@@ -6981,31 +6981,31 @@
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C21">
         <v>2023</v>
       </c>
       <c r="D21" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F21">
         <v>127150</v>
       </c>
       <c r="G21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H21" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I21" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J21" t="s">
         <v>3</v>
@@ -7014,25 +7014,25 @@
         <v>5</v>
       </c>
       <c r="M21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N21" t="s">
         <v>2</v>
       </c>
       <c r="O21" t="s">
+        <v>296</v>
+      </c>
+      <c r="P21" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q21" t="s">
         <v>298</v>
-      </c>
-      <c r="P21" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>300</v>
       </c>
       <c r="R21">
         <v>250</v>
       </c>
       <c r="T21" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U21">
         <v>15</v>
@@ -7046,31 +7046,31 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C22">
         <v>2024</v>
       </c>
       <c r="D22" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E22" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F22">
         <v>127150</v>
       </c>
       <c r="G22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H22" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I22" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J22" t="s">
         <v>3</v>
@@ -7079,25 +7079,25 @@
         <v>2</v>
       </c>
       <c r="M22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N22" t="s">
         <v>2</v>
       </c>
       <c r="O22" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P22" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q22" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R22">
         <v>208.69800000000001</v>
       </c>
       <c r="T22" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U22">
         <v>15</v>
@@ -7111,31 +7111,31 @@
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C23">
         <v>2025</v>
       </c>
       <c r="D23" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F23">
         <v>127150</v>
       </c>
       <c r="G23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H23" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I23" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J23" t="s">
         <v>3</v>
@@ -7144,25 +7144,25 @@
         <v>3</v>
       </c>
       <c r="M23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N23" t="s">
         <v>2</v>
       </c>
       <c r="O23" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P23" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q23" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R23">
         <v>42.3384</v>
       </c>
       <c r="T23" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U23">
         <v>15</v>
@@ -7176,31 +7176,31 @@
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C24">
         <v>2026</v>
       </c>
       <c r="D24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E24" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F24">
         <v>127150</v>
       </c>
       <c r="G24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H24" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I24" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J24" t="s">
         <v>3</v>
@@ -7209,25 +7209,25 @@
         <v>4</v>
       </c>
       <c r="M24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N24" t="s">
         <v>2</v>
       </c>
       <c r="O24" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P24" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q24" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R24">
         <v>17.529620000000001</v>
       </c>
       <c r="T24" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U24">
         <v>15</v>
@@ -7241,31 +7241,31 @@
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C25">
         <v>2027</v>
       </c>
       <c r="D25" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E25" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F25">
         <v>127150</v>
       </c>
       <c r="G25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H25" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I25" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J25" t="s">
         <v>3</v>
@@ -7274,25 +7274,25 @@
         <v>5</v>
       </c>
       <c r="M25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N25" t="s">
         <v>2</v>
       </c>
       <c r="O25" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P25" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q25" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R25">
         <v>11.48574</v>
       </c>
       <c r="T25" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U25">
         <v>15</v>
@@ -7306,31 +7306,31 @@
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B26" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C26">
         <v>2023</v>
       </c>
       <c r="D26" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E26" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F26">
         <v>127150</v>
       </c>
       <c r="G26" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H26" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I26" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J26" t="s">
         <v>3</v>
@@ -7339,25 +7339,25 @@
         <v>1</v>
       </c>
       <c r="M26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N26" t="s">
+        <v>295</v>
+      </c>
+      <c r="O26" t="s">
+        <v>296</v>
+      </c>
+      <c r="P26" t="s">
         <v>297</v>
       </c>
-      <c r="O26" t="s">
+      <c r="Q26" t="s">
         <v>298</v>
-      </c>
-      <c r="P26" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>300</v>
       </c>
       <c r="R26">
         <v>208.69800000000001</v>
       </c>
       <c r="T26" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U26">
         <v>15</v>
@@ -7371,31 +7371,31 @@
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C27">
         <v>2023</v>
       </c>
       <c r="D27" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E27" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F27">
         <v>127150</v>
       </c>
       <c r="G27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I27" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J27" t="s">
         <v>3</v>
@@ -7404,25 +7404,25 @@
         <v>2</v>
       </c>
       <c r="M27" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N27" t="s">
+        <v>295</v>
+      </c>
+      <c r="O27" t="s">
+        <v>296</v>
+      </c>
+      <c r="P27" t="s">
         <v>297</v>
       </c>
-      <c r="O27" t="s">
+      <c r="Q27" t="s">
         <v>298</v>
-      </c>
-      <c r="P27" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>300</v>
       </c>
       <c r="R27">
         <v>42.3384</v>
       </c>
       <c r="T27" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U27">
         <v>15</v>
@@ -7436,31 +7436,31 @@
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C28">
         <v>2023</v>
       </c>
       <c r="D28" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E28" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F28">
         <v>127150</v>
       </c>
       <c r="G28" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H28" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I28" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J28" t="s">
         <v>3</v>
@@ -7469,25 +7469,25 @@
         <v>3</v>
       </c>
       <c r="M28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N28" t="s">
+        <v>295</v>
+      </c>
+      <c r="O28" t="s">
+        <v>296</v>
+      </c>
+      <c r="P28" t="s">
         <v>297</v>
       </c>
-      <c r="O28" t="s">
+      <c r="Q28" t="s">
         <v>298</v>
-      </c>
-      <c r="P28" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>300</v>
       </c>
       <c r="R28">
         <v>17.529620000000001</v>
       </c>
       <c r="T28" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U28">
         <v>15</v>
@@ -7501,31 +7501,31 @@
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C29">
         <v>2023</v>
       </c>
       <c r="D29" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E29" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F29">
         <v>127150</v>
       </c>
       <c r="G29" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H29" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I29" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J29" t="s">
         <v>3</v>
@@ -7534,25 +7534,25 @@
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N29" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O29" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P29" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q29" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R29">
         <v>478.71000000000004</v>
       </c>
       <c r="T29" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U29">
         <v>15</v>
@@ -7566,31 +7566,31 @@
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C30">
         <v>2023</v>
       </c>
       <c r="D30" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E30" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F30">
         <v>127150</v>
       </c>
       <c r="G30" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H30" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I30" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J30" t="s">
         <v>3</v>
@@ -7599,25 +7599,25 @@
         <v>2</v>
       </c>
       <c r="M30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N30" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O30" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P30" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q30" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R30">
         <v>584.97</v>
       </c>
       <c r="T30" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U30">
         <v>15</v>
@@ -7631,31 +7631,31 @@
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B31" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C31">
         <v>2023</v>
       </c>
       <c r="D31" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F31">
         <v>127150</v>
       </c>
       <c r="G31" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H31" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I31" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J31" t="s">
         <v>3</v>
@@ -7664,25 +7664,25 @@
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N31" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O31" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P31" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q31" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R31">
         <v>907.98</v>
       </c>
       <c r="T31" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U31">
         <v>15</v>
@@ -7696,31 +7696,31 @@
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B32" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C32">
         <v>2023</v>
       </c>
       <c r="D32" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F32">
         <v>127150</v>
       </c>
       <c r="G32" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H32" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I32" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J32" t="s">
         <v>3</v>
@@ -7729,25 +7729,25 @@
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N32" t="s">
         <v>2</v>
       </c>
       <c r="O32" t="s">
+        <v>296</v>
+      </c>
+      <c r="P32" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q32" t="s">
         <v>298</v>
-      </c>
-      <c r="P32" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>300</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="T32" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U32">
         <v>15</v>
@@ -7761,31 +7761,31 @@
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C33">
         <v>2023</v>
       </c>
       <c r="D33" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E33" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F33">
         <v>127150</v>
       </c>
       <c r="G33" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H33" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I33" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J33" t="s">
         <v>3</v>
@@ -7794,25 +7794,25 @@
         <v>2</v>
       </c>
       <c r="M33" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N33" t="s">
         <v>2</v>
       </c>
       <c r="O33" t="s">
+        <v>296</v>
+      </c>
+      <c r="P33" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q33" t="s">
         <v>298</v>
-      </c>
-      <c r="P33" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>300</v>
       </c>
       <c r="R33">
         <v>150</v>
       </c>
       <c r="T33" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U33">
         <v>15</v>
@@ -7826,31 +7826,31 @@
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B34" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C34">
         <v>2023</v>
       </c>
       <c r="D34" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E34" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F34">
         <v>127150</v>
       </c>
       <c r="G34" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H34" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I34" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J34" t="s">
         <v>3</v>
@@ -7859,25 +7859,25 @@
         <v>3</v>
       </c>
       <c r="M34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N34" t="s">
         <v>2</v>
       </c>
       <c r="O34" t="s">
+        <v>296</v>
+      </c>
+      <c r="P34" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q34" t="s">
         <v>298</v>
-      </c>
-      <c r="P34" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>300</v>
       </c>
       <c r="R34">
         <v>200</v>
       </c>
       <c r="T34" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U34">
         <v>15</v>
@@ -7891,31 +7891,31 @@
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C35">
         <v>2024</v>
       </c>
       <c r="D35" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E35" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F35">
         <v>127150</v>
       </c>
       <c r="G35" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H35" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I35" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J35" t="s">
         <v>3</v>
@@ -7924,25 +7924,25 @@
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N35" t="s">
         <v>2</v>
       </c>
       <c r="O35" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P35" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q35" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R35">
         <v>208.69800000000001</v>
       </c>
       <c r="T35" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U35">
         <v>15</v>
@@ -7956,31 +7956,31 @@
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B36" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C36">
         <v>2025</v>
       </c>
       <c r="D36" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E36" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F36">
         <v>127150</v>
       </c>
       <c r="G36" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H36" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I36" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J36" t="s">
         <v>3</v>
@@ -7989,25 +7989,25 @@
         <v>2</v>
       </c>
       <c r="M36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N36" t="s">
         <v>2</v>
       </c>
       <c r="O36" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P36" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q36" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R36">
         <v>42.3384</v>
       </c>
       <c r="T36" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U36">
         <v>15</v>
@@ -8021,31 +8021,31 @@
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B37" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C37">
         <v>2026</v>
       </c>
       <c r="D37" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E37" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F37">
         <v>127150</v>
       </c>
       <c r="G37" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H37" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I37" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J37" t="s">
         <v>3</v>
@@ -8054,25 +8054,25 @@
         <v>3</v>
       </c>
       <c r="M37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N37" t="s">
         <v>2</v>
       </c>
       <c r="O37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P37" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q37" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R37">
         <v>17.529620000000001</v>
       </c>
       <c r="T37" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U37">
         <v>15</v>
@@ -8104,10 +8104,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -8118,7 +8118,7 @@
         <v>46082</v>
       </c>
       <c r="C2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -8129,7 +8129,7 @@
         <v>46126</v>
       </c>
       <c r="C3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -8138,12 +8138,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CF5149A2F9434B4282E37FA76C9DDAE3" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="926e61e4a601c985d0b7a12fe0d96524">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -8257,6 +8251,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -8267,21 +8267,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEB43D0-560F-48CD-B064-47F998E79E6D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29D1FBF4-655E-47E5-A1CE-BAFCF9C00F33}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8297,6 +8282,21 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEB43D0-560F-48CD-B064-47F998E79E6D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
   <ds:schemaRefs>

--- a/CEF and SCF formats/CEF_v17.xlsx
+++ b/CEF and SCF formats/CEF_v17.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Development\Rstudio\D1SCI\VISBIO\RDBES\CEF and SCF formats\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/kibi_dtu_dk/Documents/RDBES_gits/RDBES/CEF and SCF formats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80A4342-1631-4727-9251-CDD4AABAEBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{A80A4342-1631-4727-9251-CDD4AABAEBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2027E0FE-1F14-4A30-861A-D4B29AD3FD04}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-3105" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{C3BA46FC-17EC-4006-828F-4F15940585FB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{C3BA46FC-17EC-4006-828F-4F15940585FB}"/>
   </bookViews>
   <sheets>
     <sheet name="CEF" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="310">
   <si>
     <t>Version</t>
   </si>
@@ -590,9 +590,6 @@
     <t>Age, WidthCarapace, LengthCarapace, LengthMantle, LengthMaximumShell, LengthPreAnal, LengthPreCaudal, LengthStandard, LengthTotal</t>
   </si>
   <si>
-    <t xml:space="preserve"> wr, y, mm</t>
-  </si>
-  <si>
     <t>Sex</t>
   </si>
   <si>
@@ -698,35 +695,13 @@
     <t>Accepted codes in this field: Age, WidthCarapace, LengthCarapace, LengthMantle, LengthMaximumShell, LengthPreAnal, LengthPreCaudal, LengthStandard, LengthTotal</t>
   </si>
   <si>
-    <t>Accepted codes in this field: wr, y, mm
-If distributionType = Age --&gt; distributionUnit  = y or wr
-if distributionType != Age --&gt; distributionUnit = mm
-distributionUnit should be the same within vesselFlagCountry, year, workingGroup, stock, speciesCode, catchCategory, domainBiology and distributionType</t>
-  </si>
-  <si>
-    <t>The unit of the distributionType. 
-If distributionType = Age, then use wr or y. 
-Use 'mm' for the Length-related distribution types or WidthCarapace.</t>
-  </si>
-  <si>
     <t>if attributeType = Sex then use F= Female or M  = Male</t>
   </si>
   <si>
     <t>Accepted codes in this field: Sex</t>
   </si>
   <si>
-    <t>Accepted codes in this field: g, kg, mm, N, NE3 
-If variableType = WeightLive --&gt;variableUnit in (g,kg).
-If variableType = Number --&gt; variableUnit in (N,N3).
-If variableType in (WidthCarapace, LengthCarapace., LengthMantle, LengthMaximumShell, LengthPreAnal, LengthPreCaudal, LengthStandard, LengthTotal) --&gt; variableUnit = mm</t>
-  </si>
-  <si>
     <t>If PSU = FishingTrip, then numPSUs must equal numTrips to ensure each PSU represents exactly one trip</t>
-  </si>
-  <si>
-    <t>Accepted codes in this field:  t, kg, N, NE3. 
-If variableType = WeightLive --&gt;variableUnit in (t,kg).
-If variableType = Number --&gt; variableUnit in (N,N3).</t>
   </si>
   <si>
     <t>Count of PSUs that provided actual samples used in the estimated distribution or age–length/ age–width key, so not the total number of PSUs the estimated distribution may represent. If no actual samples were collected for a PSU (e.g., samples were borrowed to obtain the estimate), a value of 0 should be reported.</t>
@@ -852,11 +827,6 @@
   </si>
   <si>
     <t>Accepted codes in this field: CombOD, Exprt, HarbLoc, Logb, OthDF, PosDat, VMS, Unknown</t>
-  </si>
-  <si>
-    <t>Accepted codes in this field: t, kg, N, NE3
-If variableType = 'WeightLive' --&gt;variableUnit in ('t','kg').
-If variableType = 'Number --&gt; variableUnit in ('N','N3').</t>
   </si>
   <si>
     <t xml:space="preserve">Conditional check: If SeasonType = 'Month', SeasonValue uses from code type //vocab.ices.dk/?ref=1646. If SeasonType='Quarter', SeasonValue used from code type //vocab.ices.dk/?ref=1645. If SeasonType ='Year', SeasonValue uses from code type //vocab.ices.dk/?ref=362
@@ -1134,6 +1104,42 @@
   <si>
     <t>This specifies whether the total is expressed as days at sea (das), KiloWatt days at sea  (kWd-at-sea), KiloWatt Fishing days (kWd-fishing), Fishing days (fd), Number of Vessels (NoV), FishingHours (hf), Number of fishing events (fe),  Kilograms per vessel per hour (kg/vessel/h), Hook Days (hd)
 The variableType should follow what is requested  through the data call.</t>
+  </si>
+  <si>
+    <t>Accepted codes in this field:  t, kg, N, NE3. 
+If variableType = WeightLive --&gt;variableUnit in (t,kg).
+If variableType = Number --&gt; variableUnit in (N,NE3).</t>
+  </si>
+  <si>
+    <t>Accepted codes in this field: g, kg, mm, N, NE3 
+If variableType = WeightLive --&gt;variableUnit in (g,kg).
+If variableType = Number --&gt; variableUnit in (N,NE3).
+If variableType in (WidthCarapace, LengthCarapace., LengthMantle, LengthMaximumShell, LengthPreAnal, LengthPreCaudal, LengthStandard, LengthTotal) --&gt; variableUnit = mm</t>
+  </si>
+  <si>
+    <t>Accepted codes in this field: t, kg, N, NE3
+If variableType = 'WeightLive' --&gt;variableUnit in ('t','kg').
+If variableType = 'Number --&gt; variableUnit in ('N','NE3').</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nwr, y, mm</t>
+  </si>
+  <si>
+    <t>Accepted codes in this field: Nwr, y, mm
+If distributionType = Age --&gt; distributionUnit  = y or Nwr
+if distributionType != Age --&gt; distributionUnit = mm
+distributionUnit should be the same within vesselFlagCountry, year, workingGroup, stock, speciesCode, catchCategory, domainBiology and distributionType</t>
+  </si>
+  <si>
+    <t>The unit of the distributionType. 
+If distributionType = Age, then use Nwr or y. 
+Use 'mm' for the Length-related distribution types or WidthCarapace.</t>
+  </si>
+  <si>
+    <t>Code correction; N3 to NE3</t>
+  </si>
+  <si>
+    <t>Code correction; wr to Nwr</t>
   </si>
 </sst>
 </file>
@@ -1384,7 +1390,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1526,6 +1532,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1905,7 +1914,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="59" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="I2" s="15"/>
     </row>
@@ -1945,7 +1954,7 @@
       </c>
       <c r="D6" s="34"/>
       <c r="E6" s="36" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="F6" s="36" t="s">
         <v>21</v>
@@ -2347,7 +2356,7 @@
         <v>2</v>
       </c>
       <c r="M19" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="N19" t="s">
         <v>2</v>
@@ -2474,7 +2483,7 @@
       </c>
       <c r="G24" s="35"/>
       <c r="J24" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K24" t="s">
         <v>2</v>
@@ -2483,7 +2492,7 @@
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="33"/>
       <c r="B25" s="34" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C25" s="34" t="s">
         <v>2</v>
@@ -2808,7 +2817,7 @@
         <v>48</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>118</v>
@@ -2874,7 +2883,7 @@
       </c>
       <c r="I5" s="6"/>
       <c r="K5" s="7" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>142</v>
@@ -2908,7 +2917,7 @@
       <c r="I6" s="23"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>142</v>
@@ -2942,7 +2951,7 @@
       <c r="I7" s="24"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>142</v>
@@ -3011,10 +3020,10 @@
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -3040,14 +3049,14 @@
         <v>109</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="7" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="144" x14ac:dyDescent="0.3">
@@ -3074,10 +3083,10 @@
       </c>
       <c r="I11" s="20"/>
       <c r="K11" s="7" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -3106,10 +3115,10 @@
         <v>92</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="72" x14ac:dyDescent="0.3">
@@ -3136,10 +3145,10 @@
       </c>
       <c r="I13" s="6"/>
       <c r="K13" s="7" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -3196,10 +3205,10 @@
       </c>
       <c r="I15" s="6"/>
       <c r="K15" s="7" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
@@ -3219,18 +3228,18 @@
         <v>52</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
       <c r="K16" s="7" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="144" x14ac:dyDescent="0.3">
@@ -3250,16 +3259,16 @@
         <v>52</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="7" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="185.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3279,10 +3288,10 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="K18" s="7" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="185.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3302,10 +3311,10 @@
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="K19" s="7" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
@@ -3328,10 +3337,10 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="K20" s="7" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
@@ -3339,7 +3348,7 @@
         <v>51</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>47</v>
@@ -3361,10 +3370,10 @@
       </c>
       <c r="J21" s="14"/>
       <c r="K21" s="7" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="L21" s="29" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="28.8" x14ac:dyDescent="0.2">
@@ -3394,10 +3403,10 @@
       </c>
       <c r="J22" s="19"/>
       <c r="K22" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
@@ -3424,10 +3433,10 @@
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>197</v>
+        <v>185</v>
+      </c>
+      <c r="L23" s="61" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
@@ -3441,16 +3450,16 @@
         <v>2</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="K24" s="7" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -3493,14 +3502,14 @@
         <v>116</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="J26" s="14"/>
       <c r="K26" s="7" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
@@ -3518,10 +3527,10 @@
       </c>
       <c r="G27" s="7"/>
       <c r="K27" s="7" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
@@ -3539,10 +3548,10 @@
       </c>
       <c r="G28" s="7"/>
       <c r="K28" s="7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -3733,7 +3742,7 @@
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>142</v>
@@ -3767,7 +3776,7 @@
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>142</v>
@@ -3800,7 +3809,7 @@
         <v>108</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>142</v>
@@ -3870,10 +3879,10 @@
         <v>153</v>
       </c>
       <c r="J9" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>188</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>189</v>
       </c>
       <c r="L9" s="7"/>
     </row>
@@ -3898,7 +3907,7 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="7" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>149</v>
@@ -3931,10 +3940,10 @@
         <v>157</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L11" s="7"/>
     </row>
@@ -3958,14 +3967,14 @@
       <c r="H12" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="I12" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>191</v>
+      <c r="I12" s="62" t="s">
+        <v>305</v>
+      </c>
+      <c r="J12" s="61" t="s">
+        <v>307</v>
+      </c>
+      <c r="K12" s="61" t="s">
+        <v>306</v>
       </c>
       <c r="L12" s="7"/>
     </row>
@@ -3987,7 +3996,7 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -4008,10 +4017,10 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="7" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="L14" s="7"/>
     </row>
@@ -4039,13 +4048,13 @@
         <v>114</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L15" s="5"/>
     </row>
@@ -4073,13 +4082,13 @@
         <v>141</v>
       </c>
       <c r="I16" s="47" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="L16" s="5"/>
     </row>
@@ -4106,13 +4115,13 @@
         <v>114</v>
       </c>
       <c r="I17" s="48" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="L17" s="7"/>
     </row>
@@ -4137,13 +4146,13 @@
         <v>115</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>195</v>
+        <v>217</v>
+      </c>
+      <c r="K18" s="61" t="s">
+        <v>303</v>
       </c>
       <c r="L18" s="7"/>
     </row>
@@ -4168,13 +4177,13 @@
         <v>121</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="L19" s="7"/>
     </row>
@@ -4193,7 +4202,7 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="7" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -4240,13 +4249,13 @@
         <v>116</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L22" s="7"/>
     </row>
@@ -4268,7 +4277,7 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="7" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -4291,10 +4300,10 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="7" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L24" s="7"/>
     </row>
@@ -4316,7 +4325,7 @@
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
       <c r="J25" s="7" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -4532,7 +4541,7 @@
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>142</v>
@@ -4564,7 +4573,7 @@
       </c>
       <c r="H9" s="23"/>
       <c r="I9" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>142</v>
@@ -4598,7 +4607,7 @@
       </c>
       <c r="H10" s="24"/>
       <c r="I10" s="7" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>142</v>
@@ -4655,19 +4664,19 @@
         <v>52</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>73</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="27"/>
@@ -4689,19 +4698,19 @@
         <v>52</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>109</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J13" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="27"/>
@@ -4730,10 +4739,10 @@
       </c>
       <c r="H14" s="20"/>
       <c r="I14" s="7" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="27"/>
@@ -4762,10 +4771,10 @@
         <v>92</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K15" s="6"/>
       <c r="L15" s="27"/>
@@ -4794,10 +4803,10 @@
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="54" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="27"/>
@@ -4883,19 +4892,19 @@
         <v>52</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>125</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="27"/>
@@ -4949,14 +4958,14 @@
         <v>52</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="7" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
@@ -4984,7 +4993,7 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>127</v>
@@ -4997,7 +5006,7 @@
         <v>51</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>47</v>
@@ -5018,10 +5027,10 @@
         <v>156</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K23" s="7"/>
     </row>
@@ -5051,10 +5060,10 @@
         <v>154</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K24" s="6"/>
       <c r="L24" s="27"/>
@@ -5083,10 +5092,10 @@
         <v>155</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>186</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>231</v>
+        <v>185</v>
+      </c>
+      <c r="J25" s="61" t="s">
+        <v>304</v>
       </c>
       <c r="K25" s="27"/>
       <c r="L25" s="27"/>
@@ -5103,13 +5112,13 @@
         <v>2</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="27"/>
       <c r="H26" s="27"/>
       <c r="I26" s="27" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="J26" s="27"/>
       <c r="K26" s="27"/>
@@ -5268,7 +5277,7 @@
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>142</v>
@@ -5299,7 +5308,7 @@
       </c>
       <c r="H6" s="23"/>
       <c r="I6" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>142</v>
@@ -5325,19 +5334,19 @@
         <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>109</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J7" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K7" s="7"/>
     </row>
@@ -5365,10 +5374,10 @@
       </c>
       <c r="H8" s="20"/>
       <c r="I8" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K8" s="7"/>
     </row>
@@ -5398,10 +5407,10 @@
         <v>92</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K9" s="7"/>
     </row>
@@ -5428,10 +5437,10 @@
         <v>112</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K10" s="7"/>
     </row>
@@ -5513,14 +5522,14 @@
         <v>52</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="7" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J13" s="46"/>
       <c r="K13" s="7"/>
@@ -5547,7 +5556,7 @@
       <c r="G14" s="5"/>
       <c r="H14" s="14"/>
       <c r="I14" s="7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="J14" s="28"/>
       <c r="K14" s="7"/>
@@ -5557,7 +5566,7 @@
         <v>51</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>47</v>
@@ -5578,10 +5587,10 @@
         <v>156</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K15" s="7"/>
     </row>
@@ -5608,13 +5617,13 @@
         <v>115</v>
       </c>
       <c r="H16" s="60" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="J16" s="61" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="K16" s="7"/>
     </row>
@@ -5630,13 +5639,13 @@
         <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F17" s="27"/>
       <c r="G17" s="27"/>
       <c r="H17" s="27"/>
       <c r="I17" s="7" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="27"/>
@@ -5657,7 +5666,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D1" s="1"/>
     </row>
@@ -5748,7 +5757,7 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="18" x14ac:dyDescent="0.35">
@@ -5756,25 +5765,25 @@
         <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>2023</v>
       </c>
       <c r="D2" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E2" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F2">
         <v>127150</v>
       </c>
       <c r="G2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H2" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -5783,29 +5792,29 @@
         <v>92</v>
       </c>
       <c r="K2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="L2" s="56"/>
       <c r="M2" s="11" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="N2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="P2" s="56"/>
       <c r="Q2" s="56"/>
       <c r="R2" s="56"/>
       <c r="S2" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="T2" s="56" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="U2" s="56" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="V2" s="57">
         <v>377</v>
@@ -5821,22 +5830,22 @@
         <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C3">
         <v>2023</v>
       </c>
       <c r="D3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F3">
         <v>127150</v>
       </c>
       <c r="G3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="H3" t="s">
         <v>95</v>
@@ -5848,26 +5857,26 @@
         <v>92</v>
       </c>
       <c r="K3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="M3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="N3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="O3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="P3" s="1"/>
       <c r="S3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="T3" s="56" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="U3" s="56" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="V3" s="57">
         <v>15</v>
@@ -5883,22 +5892,22 @@
         <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C4">
         <v>2023</v>
       </c>
       <c r="D4" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E4" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F4">
         <v>127150</v>
       </c>
       <c r="G4" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="H4" t="s">
         <v>95</v>
@@ -5910,37 +5919,37 @@
         <v>92</v>
       </c>
       <c r="K4" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="M4" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="N4" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="O4" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="P4" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="R4" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="S4" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="T4" s="56" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="U4" s="56" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="V4" s="58">
         <v>250</v>
       </c>
       <c r="X4" s="58" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="Y4" s="58">
         <v>15</v>
@@ -5954,22 +5963,22 @@
         <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C5">
         <v>2023</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E5" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F5">
         <v>127150</v>
       </c>
       <c r="G5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H5" t="s">
         <v>95</v>
@@ -5981,31 +5990,31 @@
         <v>92</v>
       </c>
       <c r="K5" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="M5" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="N5" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="O5" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="P5" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="R5" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="S5" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="T5" s="56" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="U5" s="56" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="V5" s="58">
         <v>523</v>
@@ -6017,22 +6026,22 @@
         <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C6">
         <v>2023</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E6" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F6">
         <v>127150</v>
       </c>
       <c r="G6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H6" t="s">
         <v>95</v>
@@ -6044,31 +6053,31 @@
         <v>92</v>
       </c>
       <c r="K6" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="M6" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="N6" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="O6" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="P6" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="R6" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="S6" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="T6" s="56" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="U6" s="56" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="V6" s="58">
         <v>369</v>
@@ -6080,22 +6089,22 @@
         <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C7">
         <v>2023</v>
       </c>
       <c r="D7" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E7" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F7">
         <v>127150</v>
       </c>
       <c r="G7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H7" t="s">
         <v>95</v>
@@ -6107,31 +6116,31 @@
         <v>92</v>
       </c>
       <c r="K7" t="s">
+        <v>270</v>
+      </c>
+      <c r="M7" t="s">
+        <v>279</v>
+      </c>
+      <c r="N7" t="s">
+        <v>272</v>
+      </c>
+      <c r="O7" t="s">
+        <v>280</v>
+      </c>
+      <c r="P7" t="s">
+        <v>283</v>
+      </c>
+      <c r="R7" t="s">
+        <v>283</v>
+      </c>
+      <c r="S7" t="s">
+        <v>274</v>
+      </c>
+      <c r="T7" s="56" t="s">
+        <v>275</v>
+      </c>
+      <c r="U7" s="56" t="s">
         <v>276</v>
-      </c>
-      <c r="M7" t="s">
-        <v>285</v>
-      </c>
-      <c r="N7" t="s">
-        <v>278</v>
-      </c>
-      <c r="O7" t="s">
-        <v>286</v>
-      </c>
-      <c r="P7" t="s">
-        <v>289</v>
-      </c>
-      <c r="R7" t="s">
-        <v>289</v>
-      </c>
-      <c r="S7" t="s">
-        <v>280</v>
-      </c>
-      <c r="T7" s="56" t="s">
-        <v>281</v>
-      </c>
-      <c r="U7" s="56" t="s">
-        <v>282</v>
       </c>
       <c r="V7" s="58">
         <v>2547</v>
@@ -6143,22 +6152,22 @@
         <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C8">
         <v>2023</v>
       </c>
       <c r="D8" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E8" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F8">
         <v>127150</v>
       </c>
       <c r="G8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H8" t="s">
         <v>95</v>
@@ -6170,31 +6179,31 @@
         <v>92</v>
       </c>
       <c r="K8" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="M8" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="N8" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="O8" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="P8" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="R8" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="S8" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="T8" s="56" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="U8" s="56" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="V8" s="58">
         <v>236</v>
@@ -6206,22 +6215,22 @@
         <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C9">
         <v>2023</v>
       </c>
       <c r="D9" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E9" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F9">
         <v>127150</v>
       </c>
       <c r="G9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H9" t="s">
         <v>95</v>
@@ -6233,31 +6242,31 @@
         <v>92</v>
       </c>
       <c r="K9" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="M9" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="N9" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="O9" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="P9" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="R9" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="S9" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="T9" s="56" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="U9" s="56" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="V9" s="58">
         <v>2589</v>
@@ -6269,28 +6278,28 @@
         <v>128</v>
       </c>
       <c r="B10" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C10">
         <v>2023</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E10" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F10">
         <v>127150</v>
       </c>
       <c r="G10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H10" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I10" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J10" t="s">
         <v>3</v>
@@ -6299,25 +6308,25 @@
         <v>2</v>
       </c>
       <c r="M10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N10" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="O10" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P10" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q10" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R10">
         <v>208.69800000000001</v>
       </c>
       <c r="T10" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U10">
         <v>15</v>
@@ -6334,28 +6343,28 @@
         <v>128</v>
       </c>
       <c r="B11" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C11">
         <v>2023</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E11" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F11">
         <v>127150</v>
       </c>
       <c r="G11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H11" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I11" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J11" t="s">
         <v>3</v>
@@ -6364,25 +6373,25 @@
         <v>3</v>
       </c>
       <c r="M11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N11" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="O11" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P11" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q11" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R11">
         <v>42.3384</v>
       </c>
       <c r="T11" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U11">
         <v>15</v>
@@ -6399,28 +6408,28 @@
         <v>128</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C12">
         <v>2023</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E12" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F12">
         <v>127150</v>
       </c>
       <c r="G12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H12" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I12" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J12" t="s">
         <v>3</v>
@@ -6429,25 +6438,25 @@
         <v>4</v>
       </c>
       <c r="M12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N12" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="O12" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P12" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q12" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R12">
         <v>17.529620000000001</v>
       </c>
       <c r="T12" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U12">
         <v>15</v>
@@ -6464,28 +6473,28 @@
         <v>128</v>
       </c>
       <c r="B13" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C13">
         <v>2023</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E13" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F13">
         <v>127150</v>
       </c>
       <c r="G13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H13" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I13" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J13" t="s">
         <v>3</v>
@@ -6494,25 +6503,25 @@
         <v>5</v>
       </c>
       <c r="M13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="O13" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P13" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q13" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R13">
         <v>11.48574</v>
       </c>
       <c r="T13" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U13">
         <v>15</v>
@@ -6529,28 +6538,28 @@
         <v>128</v>
       </c>
       <c r="B14" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C14">
         <v>2023</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E14" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F14">
         <v>127150</v>
       </c>
       <c r="G14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H14" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I14" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J14" t="s">
         <v>3</v>
@@ -6559,25 +6568,25 @@
         <v>2</v>
       </c>
       <c r="M14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N14" t="s">
+        <v>289</v>
+      </c>
+      <c r="O14" t="s">
+        <v>275</v>
+      </c>
+      <c r="P14" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q14" t="s">
         <v>295</v>
-      </c>
-      <c r="O14" t="s">
-        <v>281</v>
-      </c>
-      <c r="P14" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>301</v>
       </c>
       <c r="R14">
         <v>478.71000000000004</v>
       </c>
       <c r="T14" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U14">
         <v>15</v>
@@ -6594,28 +6603,28 @@
         <v>128</v>
       </c>
       <c r="B15" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C15">
         <v>2023</v>
       </c>
       <c r="D15" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E15" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F15">
         <v>127150</v>
       </c>
       <c r="G15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I15" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J15" t="s">
         <v>3</v>
@@ -6624,25 +6633,25 @@
         <v>3</v>
       </c>
       <c r="M15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N15" t="s">
+        <v>289</v>
+      </c>
+      <c r="O15" t="s">
+        <v>275</v>
+      </c>
+      <c r="P15" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q15" t="s">
         <v>295</v>
-      </c>
-      <c r="O15" t="s">
-        <v>281</v>
-      </c>
-      <c r="P15" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>301</v>
       </c>
       <c r="R15">
         <v>584.97</v>
       </c>
       <c r="T15" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U15">
         <v>15</v>
@@ -6659,28 +6668,28 @@
         <v>128</v>
       </c>
       <c r="B16" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C16">
         <v>2023</v>
       </c>
       <c r="D16" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E16" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F16">
         <v>127150</v>
       </c>
       <c r="G16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H16" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I16" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J16" t="s">
         <v>3</v>
@@ -6689,25 +6698,25 @@
         <v>4</v>
       </c>
       <c r="M16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N16" t="s">
+        <v>289</v>
+      </c>
+      <c r="O16" t="s">
+        <v>275</v>
+      </c>
+      <c r="P16" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q16" t="s">
         <v>295</v>
-      </c>
-      <c r="O16" t="s">
-        <v>281</v>
-      </c>
-      <c r="P16" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>301</v>
       </c>
       <c r="R16">
         <v>907.98</v>
       </c>
       <c r="T16" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U16">
         <v>15</v>
@@ -6724,28 +6733,28 @@
         <v>128</v>
       </c>
       <c r="B17" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C17">
         <v>2023</v>
       </c>
       <c r="D17" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E17" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F17">
         <v>127150</v>
       </c>
       <c r="G17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H17" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I17" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J17" t="s">
         <v>3</v>
@@ -6754,25 +6763,25 @@
         <v>5</v>
       </c>
       <c r="M17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N17" t="s">
+        <v>289</v>
+      </c>
+      <c r="O17" t="s">
+        <v>275</v>
+      </c>
+      <c r="P17" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q17" t="s">
         <v>295</v>
-      </c>
-      <c r="O17" t="s">
-        <v>281</v>
-      </c>
-      <c r="P17" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>301</v>
       </c>
       <c r="R17">
         <v>1290.6899999999998</v>
       </c>
       <c r="T17" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U17">
         <v>15</v>
@@ -6789,28 +6798,28 @@
         <v>128</v>
       </c>
       <c r="B18" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C18">
         <v>2023</v>
       </c>
       <c r="D18" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E18" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F18">
         <v>127150</v>
       </c>
       <c r="G18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H18" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I18" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J18" t="s">
         <v>3</v>
@@ -6819,25 +6828,25 @@
         <v>2</v>
       </c>
       <c r="M18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N18" t="s">
         <v>2</v>
       </c>
       <c r="O18" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P18" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q18" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="T18" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U18">
         <v>15</v>
@@ -6854,28 +6863,28 @@
         <v>128</v>
       </c>
       <c r="B19" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C19">
         <v>2023</v>
       </c>
       <c r="D19" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E19" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F19">
         <v>127150</v>
       </c>
       <c r="G19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H19" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I19" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J19" t="s">
         <v>3</v>
@@ -6884,25 +6893,25 @@
         <v>3</v>
       </c>
       <c r="M19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N19" t="s">
         <v>2</v>
       </c>
       <c r="O19" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P19" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q19" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R19">
         <v>150</v>
       </c>
       <c r="T19" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U19">
         <v>15</v>
@@ -6919,28 +6928,28 @@
         <v>128</v>
       </c>
       <c r="B20" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C20">
         <v>2023</v>
       </c>
       <c r="D20" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E20" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F20">
         <v>127150</v>
       </c>
       <c r="G20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H20" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I20" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J20" t="s">
         <v>3</v>
@@ -6949,25 +6958,25 @@
         <v>4</v>
       </c>
       <c r="M20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N20" t="s">
         <v>2</v>
       </c>
       <c r="O20" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P20" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q20" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R20">
         <v>200</v>
       </c>
       <c r="T20" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U20">
         <v>15</v>
@@ -6984,28 +6993,28 @@
         <v>128</v>
       </c>
       <c r="B21" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C21">
         <v>2023</v>
       </c>
       <c r="D21" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E21" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F21">
         <v>127150</v>
       </c>
       <c r="G21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H21" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I21" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J21" t="s">
         <v>3</v>
@@ -7014,25 +7023,25 @@
         <v>5</v>
       </c>
       <c r="M21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N21" t="s">
         <v>2</v>
       </c>
       <c r="O21" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P21" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q21" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R21">
         <v>250</v>
       </c>
       <c r="T21" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U21">
         <v>15</v>
@@ -7049,28 +7058,28 @@
         <v>128</v>
       </c>
       <c r="B22" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C22">
         <v>2024</v>
       </c>
       <c r="D22" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E22" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F22">
         <v>127150</v>
       </c>
       <c r="G22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H22" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I22" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J22" t="s">
         <v>3</v>
@@ -7079,25 +7088,25 @@
         <v>2</v>
       </c>
       <c r="M22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N22" t="s">
         <v>2</v>
       </c>
       <c r="O22" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="P22" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="Q22" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="R22">
         <v>208.69800000000001</v>
       </c>
       <c r="T22" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U22">
         <v>15</v>
@@ -7114,28 +7123,28 @@
         <v>128</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C23">
         <v>2025</v>
       </c>
       <c r="D23" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E23" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F23">
         <v>127150</v>
       </c>
       <c r="G23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H23" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I23" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J23" t="s">
         <v>3</v>
@@ -7144,25 +7153,25 @@
         <v>3</v>
       </c>
       <c r="M23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N23" t="s">
         <v>2</v>
       </c>
       <c r="O23" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="P23" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="Q23" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="R23">
         <v>42.3384</v>
       </c>
       <c r="T23" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U23">
         <v>15</v>
@@ -7179,28 +7188,28 @@
         <v>128</v>
       </c>
       <c r="B24" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C24">
         <v>2026</v>
       </c>
       <c r="D24" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E24" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F24">
         <v>127150</v>
       </c>
       <c r="G24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H24" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I24" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J24" t="s">
         <v>3</v>
@@ -7209,25 +7218,25 @@
         <v>4</v>
       </c>
       <c r="M24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N24" t="s">
         <v>2</v>
       </c>
       <c r="O24" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="P24" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="Q24" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="R24">
         <v>17.529620000000001</v>
       </c>
       <c r="T24" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U24">
         <v>15</v>
@@ -7244,28 +7253,28 @@
         <v>128</v>
       </c>
       <c r="B25" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C25">
         <v>2027</v>
       </c>
       <c r="D25" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E25" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F25">
         <v>127150</v>
       </c>
       <c r="G25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H25" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I25" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J25" t="s">
         <v>3</v>
@@ -7274,25 +7283,25 @@
         <v>5</v>
       </c>
       <c r="M25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N25" t="s">
         <v>2</v>
       </c>
       <c r="O25" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="P25" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="Q25" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="R25">
         <v>11.48574</v>
       </c>
       <c r="T25" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U25">
         <v>15</v>
@@ -7309,28 +7318,28 @@
         <v>128</v>
       </c>
       <c r="B26" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C26">
         <v>2023</v>
       </c>
       <c r="D26" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E26" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F26">
         <v>127150</v>
       </c>
       <c r="G26" t="s">
+        <v>277</v>
+      </c>
+      <c r="H26" t="s">
         <v>283</v>
       </c>
-      <c r="H26" t="s">
-        <v>289</v>
-      </c>
       <c r="I26" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J26" t="s">
         <v>3</v>
@@ -7339,25 +7348,25 @@
         <v>1</v>
       </c>
       <c r="M26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N26" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="O26" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P26" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q26" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R26">
         <v>208.69800000000001</v>
       </c>
       <c r="T26" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U26">
         <v>15</v>
@@ -7374,28 +7383,28 @@
         <v>128</v>
       </c>
       <c r="B27" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C27">
         <v>2023</v>
       </c>
       <c r="D27" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E27" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F27">
         <v>127150</v>
       </c>
       <c r="G27" t="s">
+        <v>277</v>
+      </c>
+      <c r="H27" t="s">
         <v>283</v>
       </c>
-      <c r="H27" t="s">
-        <v>289</v>
-      </c>
       <c r="I27" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J27" t="s">
         <v>3</v>
@@ -7404,25 +7413,25 @@
         <v>2</v>
       </c>
       <c r="M27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N27" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="O27" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P27" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q27" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R27">
         <v>42.3384</v>
       </c>
       <c r="T27" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U27">
         <v>15</v>
@@ -7439,28 +7448,28 @@
         <v>128</v>
       </c>
       <c r="B28" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C28">
         <v>2023</v>
       </c>
       <c r="D28" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E28" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F28">
         <v>127150</v>
       </c>
       <c r="G28" t="s">
+        <v>277</v>
+      </c>
+      <c r="H28" t="s">
         <v>283</v>
       </c>
-      <c r="H28" t="s">
-        <v>289</v>
-      </c>
       <c r="I28" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J28" t="s">
         <v>3</v>
@@ -7469,25 +7478,25 @@
         <v>3</v>
       </c>
       <c r="M28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N28" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="O28" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P28" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q28" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R28">
         <v>17.529620000000001</v>
       </c>
       <c r="T28" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U28">
         <v>15</v>
@@ -7504,28 +7513,28 @@
         <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C29">
         <v>2023</v>
       </c>
       <c r="D29" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E29" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F29">
         <v>127150</v>
       </c>
       <c r="G29" t="s">
+        <v>277</v>
+      </c>
+      <c r="H29" t="s">
         <v>283</v>
       </c>
-      <c r="H29" t="s">
-        <v>289</v>
-      </c>
       <c r="I29" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J29" t="s">
         <v>3</v>
@@ -7534,25 +7543,25 @@
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N29" t="s">
+        <v>289</v>
+      </c>
+      <c r="O29" t="s">
+        <v>275</v>
+      </c>
+      <c r="P29" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q29" t="s">
         <v>295</v>
-      </c>
-      <c r="O29" t="s">
-        <v>281</v>
-      </c>
-      <c r="P29" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>301</v>
       </c>
       <c r="R29">
         <v>478.71000000000004</v>
       </c>
       <c r="T29" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U29">
         <v>15</v>
@@ -7569,28 +7578,28 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C30">
         <v>2023</v>
       </c>
       <c r="D30" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E30" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F30">
         <v>127150</v>
       </c>
       <c r="G30" t="s">
+        <v>277</v>
+      </c>
+      <c r="H30" t="s">
         <v>283</v>
       </c>
-      <c r="H30" t="s">
-        <v>289</v>
-      </c>
       <c r="I30" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J30" t="s">
         <v>3</v>
@@ -7599,25 +7608,25 @@
         <v>2</v>
       </c>
       <c r="M30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N30" t="s">
+        <v>289</v>
+      </c>
+      <c r="O30" t="s">
+        <v>275</v>
+      </c>
+      <c r="P30" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q30" t="s">
         <v>295</v>
-      </c>
-      <c r="O30" t="s">
-        <v>281</v>
-      </c>
-      <c r="P30" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>301</v>
       </c>
       <c r="R30">
         <v>584.97</v>
       </c>
       <c r="T30" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U30">
         <v>15</v>
@@ -7634,28 +7643,28 @@
         <v>128</v>
       </c>
       <c r="B31" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C31">
         <v>2023</v>
       </c>
       <c r="D31" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E31" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F31">
         <v>127150</v>
       </c>
       <c r="G31" t="s">
+        <v>277</v>
+      </c>
+      <c r="H31" t="s">
         <v>283</v>
       </c>
-      <c r="H31" t="s">
-        <v>289</v>
-      </c>
       <c r="I31" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J31" t="s">
         <v>3</v>
@@ -7664,25 +7673,25 @@
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N31" t="s">
+        <v>289</v>
+      </c>
+      <c r="O31" t="s">
+        <v>275</v>
+      </c>
+      <c r="P31" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q31" t="s">
         <v>295</v>
-      </c>
-      <c r="O31" t="s">
-        <v>281</v>
-      </c>
-      <c r="P31" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>301</v>
       </c>
       <c r="R31">
         <v>907.98</v>
       </c>
       <c r="T31" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U31">
         <v>15</v>
@@ -7699,28 +7708,28 @@
         <v>128</v>
       </c>
       <c r="B32" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C32">
         <v>2023</v>
       </c>
       <c r="D32" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E32" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F32">
         <v>127150</v>
       </c>
       <c r="G32" t="s">
+        <v>277</v>
+      </c>
+      <c r="H32" t="s">
         <v>283</v>
       </c>
-      <c r="H32" t="s">
-        <v>289</v>
-      </c>
       <c r="I32" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J32" t="s">
         <v>3</v>
@@ -7729,25 +7738,25 @@
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N32" t="s">
         <v>2</v>
       </c>
       <c r="O32" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P32" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q32" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="T32" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U32">
         <v>15</v>
@@ -7764,28 +7773,28 @@
         <v>128</v>
       </c>
       <c r="B33" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C33">
         <v>2023</v>
       </c>
       <c r="D33" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E33" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F33">
         <v>127150</v>
       </c>
       <c r="G33" t="s">
+        <v>277</v>
+      </c>
+      <c r="H33" t="s">
         <v>283</v>
       </c>
-      <c r="H33" t="s">
-        <v>289</v>
-      </c>
       <c r="I33" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J33" t="s">
         <v>3</v>
@@ -7794,25 +7803,25 @@
         <v>2</v>
       </c>
       <c r="M33" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N33" t="s">
         <v>2</v>
       </c>
       <c r="O33" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P33" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q33" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R33">
         <v>150</v>
       </c>
       <c r="T33" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U33">
         <v>15</v>
@@ -7829,28 +7838,28 @@
         <v>128</v>
       </c>
       <c r="B34" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C34">
         <v>2023</v>
       </c>
       <c r="D34" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E34" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F34">
         <v>127150</v>
       </c>
       <c r="G34" t="s">
+        <v>277</v>
+      </c>
+      <c r="H34" t="s">
         <v>283</v>
       </c>
-      <c r="H34" t="s">
-        <v>289</v>
-      </c>
       <c r="I34" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J34" t="s">
         <v>3</v>
@@ -7859,25 +7868,25 @@
         <v>3</v>
       </c>
       <c r="M34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N34" t="s">
         <v>2</v>
       </c>
       <c r="O34" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P34" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q34" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R34">
         <v>200</v>
       </c>
       <c r="T34" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U34">
         <v>15</v>
@@ -7894,28 +7903,28 @@
         <v>128</v>
       </c>
       <c r="B35" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C35">
         <v>2024</v>
       </c>
       <c r="D35" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E35" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F35">
         <v>127150</v>
       </c>
       <c r="G35" t="s">
+        <v>277</v>
+      </c>
+      <c r="H35" t="s">
         <v>283</v>
       </c>
-      <c r="H35" t="s">
-        <v>289</v>
-      </c>
       <c r="I35" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J35" t="s">
         <v>3</v>
@@ -7924,25 +7933,25 @@
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N35" t="s">
         <v>2</v>
       </c>
       <c r="O35" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="P35" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="Q35" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="R35">
         <v>208.69800000000001</v>
       </c>
       <c r="T35" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U35">
         <v>15</v>
@@ -7959,28 +7968,28 @@
         <v>128</v>
       </c>
       <c r="B36" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C36">
         <v>2025</v>
       </c>
       <c r="D36" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E36" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F36">
         <v>127150</v>
       </c>
       <c r="G36" t="s">
+        <v>277</v>
+      </c>
+      <c r="H36" t="s">
         <v>283</v>
       </c>
-      <c r="H36" t="s">
-        <v>289</v>
-      </c>
       <c r="I36" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J36" t="s">
         <v>3</v>
@@ -7989,25 +7998,25 @@
         <v>2</v>
       </c>
       <c r="M36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N36" t="s">
         <v>2</v>
       </c>
       <c r="O36" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="P36" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="Q36" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="R36">
         <v>42.3384</v>
       </c>
       <c r="T36" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U36">
         <v>15</v>
@@ -8024,28 +8033,28 @@
         <v>128</v>
       </c>
       <c r="B37" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C37">
         <v>2026</v>
       </c>
       <c r="D37" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E37" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F37">
         <v>127150</v>
       </c>
       <c r="G37" t="s">
+        <v>277</v>
+      </c>
+      <c r="H37" t="s">
         <v>283</v>
       </c>
-      <c r="H37" t="s">
-        <v>289</v>
-      </c>
       <c r="I37" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J37" t="s">
         <v>3</v>
@@ -8054,25 +8063,25 @@
         <v>3</v>
       </c>
       <c r="M37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N37" t="s">
         <v>2</v>
       </c>
       <c r="O37" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="P37" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="Q37" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="R37">
         <v>17.529620000000001</v>
       </c>
       <c r="T37" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U37">
         <v>15</v>
@@ -8091,7 +8100,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C252F49-FECA-4CFA-AD70-037B1BFFBBFE}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
@@ -8104,10 +8113,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -8118,7 +8127,7 @@
         <v>46082</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -8129,7 +8138,29 @@
         <v>46126</v>
       </c>
       <c r="C3" t="s">
-        <v>304</v>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>17</v>
+      </c>
+      <c r="B4" s="55">
+        <v>46134</v>
+      </c>
+      <c r="C4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>17</v>
+      </c>
+      <c r="B5" s="55">
+        <v>46134</v>
+      </c>
+      <c r="C5" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -8138,6 +8169,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CF5149A2F9434B4282E37FA76C9DDAE3" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="926e61e4a601c985d0b7a12fe0d96524">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -8251,33 +8297,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29D1FBF4-655E-47E5-A1CE-BAFCF9C00F33}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8298,9 +8321,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29D1FBF4-655E-47E5-A1CE-BAFCF9C00F33}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>